--- a/جدول الحضور-1.xlsx
+++ b/جدول الحضور-1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\E.POINT\Desktop\عيد العرش 2026 جهاد\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C67DE07D-429D-4D95-BA17-360B10653B26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9372E73-535B-4DDD-8BA3-8B31F64616C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{23743375-DD87-4C55-8B35-0449ADC5216E}"/>
+    <workbookView xWindow="1380" yWindow="660" windowWidth="10752" windowHeight="8964" xr2:uid="{23743375-DD87-4C55-8B35-0449ADC5216E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="336">
   <si>
     <t>الصفه</t>
   </si>
@@ -45,9 +45,6 @@
     <t>المدير العام لوكالة الأنباء الليبية</t>
   </si>
   <si>
-    <t>معالى وزير الحكم المحلي</t>
-  </si>
-  <si>
     <t>السيد سامي الضاوي</t>
   </si>
   <si>
@@ -261,9 +258,6 @@
     <t>السيد معاذ بن سليم</t>
   </si>
   <si>
-    <t>المستشار عبد الحفيظ التاجوري</t>
-  </si>
-  <si>
     <t>السيدة  رابحة محمود الفارسي</t>
   </si>
   <si>
@@ -282,9 +276,6 @@
     <t>السيد علي رضا يلماز</t>
   </si>
   <si>
-    <t>السيدة تبسم منصور</t>
-  </si>
-  <si>
     <t>السيد عز الدين العبار</t>
   </si>
   <si>
@@ -330,9 +321,6 @@
     <t>نائب المدير العام لشركة القابضة</t>
   </si>
   <si>
-    <t>مدير مكتب المستشارين بوزارة الخارجية</t>
-  </si>
-  <si>
     <t>مديرة منظمات المجتمع المدني بوزارة الخارجية والتعاون الدولي</t>
   </si>
   <si>
@@ -381,9 +369,6 @@
     <t>السيد سامي بورجعة</t>
   </si>
   <si>
-    <t>سعد مفتاح الورفلي السيد</t>
-  </si>
-  <si>
     <t xml:space="preserve"> مستشار اللواء عون إبراهيم سالم الفرجاني</t>
   </si>
   <si>
@@ -405,9 +390,6 @@
     <t>الدكتور عمران بوقرين</t>
   </si>
   <si>
-    <t>الدكتور مهند لعريبي</t>
-  </si>
-  <si>
     <t>الدكتور مفتاح الفلاح</t>
   </si>
   <si>
@@ -429,9 +411,6 @@
     <t>السيد حمزة اسباقة</t>
   </si>
   <si>
-    <t>العقيد محمد أحمد  العزابي</t>
-  </si>
-  <si>
     <t>رئيس الديوان بادارة الشوؤن الاجتماعية بالقيادة العامة</t>
   </si>
   <si>
@@ -543,9 +522,6 @@
     <t>السيد نزار محمد المتجول</t>
   </si>
   <si>
-    <t>السيد ياسين عبد القادر</t>
-  </si>
-  <si>
     <t>السيد عياد العبار</t>
   </si>
   <si>
@@ -843,9 +819,6 @@
     <t>أرقام الجلوس</t>
   </si>
   <si>
-    <t>السيد ابراهيم هدية المجبري</t>
-  </si>
-  <si>
     <t>السيد يوسف ابراهيم العقوري</t>
   </si>
   <si>
@@ -882,12 +855,6 @@
     <t>السيد ادريس الطرشاني</t>
   </si>
   <si>
-    <t>السيد امجد الورفلي</t>
-  </si>
-  <si>
-    <t>العقيد السيد احمد إبراهيم البنوني</t>
-  </si>
-  <si>
     <t>السيدة امينة زوبي</t>
   </si>
   <si>
@@ -918,14 +885,170 @@
     <t>السيد احمد عبد القادر بن عمران</t>
   </si>
   <si>
-    <t>السيد ابراهيم المفتي</t>
+    <t>السيد إبراهيم هدية المجبري</t>
+  </si>
+  <si>
+    <t>معالي وزير الحكم المحلي</t>
+  </si>
+  <si>
+    <t>الدكتور إدريس حفيظة المبروك</t>
+  </si>
+  <si>
+    <t>رئيس مجلس الإدارة والمدير العام لصندوق الضمان الاجتماعي</t>
+  </si>
+  <si>
+    <t>السفير عبد المجيد غيث سيف نصر</t>
+  </si>
+  <si>
+    <t>مبعوث مجلس النواب الليبي لدول المغرب العربي</t>
+  </si>
+  <si>
+    <t>السيد حافظ مصطفى الصادق</t>
+  </si>
+  <si>
+    <t>مستشار</t>
+  </si>
+  <si>
+    <t>الدكتور مفتاح اطويلب</t>
+  </si>
+  <si>
+    <t>وكيل التعاون الدولي ومدير ضمان الجودة والاعتماد بالجامعة الليبية الدولية، والمدير العام للمركز الوطني لتطوير النظام الصحي</t>
+  </si>
+  <si>
+    <t>السيد محمد ابراهيم اسماعيل تامر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عضو مجلس النواب وعضو لجنة الصداقة المغربية الليبية بمجلس النواب الليبي </t>
+  </si>
+  <si>
+    <t>السيدة صباح جمعة محمد الحاج</t>
+  </si>
+  <si>
+    <t>عضو مجلس النواب وعضو لجنة الصداقة المغربية الليبية بمجلس النواب الليبي</t>
+  </si>
+  <si>
+    <t>السيد عيسى محمد السنوسي</t>
+  </si>
+  <si>
+    <t>زوجة مدير مركز اللغات بجامعة بنغازي</t>
+  </si>
+  <si>
+    <t>الدكتور عبد المطلوب أحمد بوفروة</t>
+  </si>
+  <si>
+    <t>رئيس جامعة عمر المختار</t>
+  </si>
+  <si>
+    <t>السيد سعد مفتاح الورفلي</t>
+  </si>
+  <si>
+    <t>السيد حاتم عبدالله حور السنوسي</t>
+  </si>
+  <si>
+    <t>ملحق سياسي بمكتب المستشارين بوزارة الخارجية</t>
+  </si>
+  <si>
+    <t>الدكتور مهند العريبي</t>
+  </si>
+  <si>
+    <t>العقيد محمد احمد  العزابي</t>
+  </si>
+  <si>
+    <t>مديرة مدرسة الحصاد الدولية ببنغازي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">السيدة تبسم منصور </t>
+  </si>
+  <si>
+    <t>السيد أمجد الورفلي</t>
+  </si>
+  <si>
+    <t>المهندس محمد الحصادي</t>
+  </si>
+  <si>
+    <t>مدير المشروعات بصندوق التنمية واعادة اعمار ليبيا</t>
+  </si>
+  <si>
+    <t>الأستاذ عبدالفتاح محمد سعد العلام</t>
+  </si>
+  <si>
+    <t>مدير إدارة التخطيط والمتابعة بالجامعة</t>
+  </si>
+  <si>
+    <t>السيد  زيدان خليفه البدري</t>
+  </si>
+  <si>
+    <t>رئيس وحدة العلاقات العامة بصندوق الضمان الاجتماعي</t>
+  </si>
+  <si>
+    <t>العقيد السيد  أحمد إبراهيم البنوني</t>
+  </si>
+  <si>
+    <t>السيد إبراهيم المفتي</t>
+  </si>
+  <si>
+    <t>السيد احمد المشيطي</t>
+  </si>
+  <si>
+    <t>مدير العلاقات الدولية الخارجية بصندوق  الاجتماعي الليبي</t>
+  </si>
+  <si>
+    <t>الصف التاسع</t>
+  </si>
+  <si>
+    <t>الدكتور أشرف بدر</t>
+  </si>
+  <si>
+    <t>السيد سامى الناجى بوزيد</t>
+  </si>
+  <si>
+    <t>نائب المدير العام لمركز BLS لتأشيرات الإسبانية فرع بنغازى</t>
+  </si>
+  <si>
+    <t>السيد مفتاح شعبان الحاسي</t>
+  </si>
+  <si>
+    <t>مشرف عام برج جوهرة بنغازي</t>
+  </si>
+  <si>
+    <t>السيد جلال أحمد بوقرين</t>
+  </si>
+  <si>
+    <t>مدير  صندوق الضمان الاجتماعي فرع غرب بنغازي</t>
+  </si>
+  <si>
+    <t>السيد هشام الرك</t>
+  </si>
+  <si>
+    <t>مدير مكتب المدير العام لشركة فرقدان</t>
+  </si>
+  <si>
+    <t>السيد Mohamed JEGHLLQLY</t>
+  </si>
+  <si>
+    <t>الأنسة  حنين الجطيوه</t>
+  </si>
+  <si>
+    <t>السيدة رشيدة العرش</t>
+  </si>
+  <si>
+    <t>السيد خليفة المغربي</t>
+  </si>
+  <si>
+    <t>السيد خالد المصراتي</t>
+  </si>
+  <si>
+    <t>الدكتور حسن الحبوني</t>
+  </si>
+  <si>
+    <t>موظف بوزارة الكهرباء والطاقات المتجددة بالحكومة الليبية</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -953,16 +1076,57 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="15"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -1099,11 +1263,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
@@ -1177,6 +1365,42 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1492,19 +1716,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18A94353-2125-49E6-91ED-D3B1232B2558}">
-  <dimension ref="A1:F187"/>
+  <dimension ref="A1:F201"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.88671875" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8.88671875" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="49.44140625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="66.109375" style="6" customWidth="1"/>
     <col min="4" max="4" width="41" style="6" customWidth="1"/>
     <col min="5" max="5" width="9.88671875" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C1" s="20" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D1" s="20"/>
       <c r="E1" s="20"/>
@@ -1517,81 +1741,81 @@
         <v>1</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="3" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C3" s="8" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="3" spans="3:5" ht="39" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="11" t="s">
-        <v>269</v>
-      </c>
-      <c r="E3" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C4" s="8" t="s">
+      <c r="D4" s="28" t="s">
+        <v>283</v>
+      </c>
+      <c r="E4" s="28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C5" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D5" s="28" t="s">
         <v>3</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C5" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>6</v>
       </c>
       <c r="E5" s="11">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="3:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C6" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>8</v>
+    <row r="6" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="28" t="s">
+        <v>5</v>
       </c>
       <c r="E6" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="28" t="s">
         <v>9</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>10</v>
       </c>
       <c r="E7" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="3:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="28" t="s">
         <v>11</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>12</v>
       </c>
       <c r="E8" s="11">
         <v>6</v>
       </c>
     </row>
     <row r="9" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="28" t="s">
         <v>13</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>14</v>
       </c>
       <c r="E9" s="11">
         <v>7</v>
@@ -1599,10 +1823,10 @@
     </row>
     <row r="10" spans="3:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C10" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="E10" s="11">
         <v>8</v>
@@ -1610,10 +1834,10 @@
     </row>
     <row r="11" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C11" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="11" t="s">
         <v>16</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>17</v>
       </c>
       <c r="E11" s="11">
         <v>9</v>
@@ -1621,10 +1845,10 @@
     </row>
     <row r="12" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C12" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="11" t="s">
         <v>18</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>19</v>
       </c>
       <c r="E12" s="11">
         <v>10</v>
@@ -1632,10 +1856,10 @@
     </row>
     <row r="13" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C13" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="11" t="s">
         <v>20</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>21</v>
       </c>
       <c r="E13" s="11">
         <v>11</v>
@@ -1643,10 +1867,10 @@
     </row>
     <row r="14" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C14" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="11" t="s">
         <v>22</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>23</v>
       </c>
       <c r="E14" s="11">
         <v>12</v>
@@ -1654,10 +1878,10 @@
     </row>
     <row r="15" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C15" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" s="11" t="s">
         <v>24</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>25</v>
       </c>
       <c r="E15" s="11">
         <v>13</v>
@@ -1665,10 +1889,10 @@
     </row>
     <row r="16" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C16" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" s="11" t="s">
         <v>26</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>27</v>
       </c>
       <c r="E16" s="11">
         <v>14</v>
@@ -1676,10 +1900,10 @@
     </row>
     <row r="17" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C17" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" s="13" t="s">
         <v>28</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>29</v>
       </c>
       <c r="E17" s="13">
         <v>15</v>
@@ -1687,17 +1911,17 @@
     </row>
     <row r="18" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C18" s="20" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D18" s="20"/>
       <c r="E18" s="20"/>
     </row>
     <row r="19" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C19" s="14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E19" s="15">
         <v>16</v>
@@ -1705,10 +1929,10 @@
     </row>
     <row r="20" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C20" s="15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="E20" s="15">
         <v>17</v>
@@ -1716,10 +1940,10 @@
     </row>
     <row r="21" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C21" s="15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E21" s="15">
         <v>18</v>
@@ -1727,10 +1951,10 @@
     </row>
     <row r="22" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C22" s="15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E22" s="15">
         <v>19</v>
@@ -1738,10 +1962,10 @@
     </row>
     <row r="23" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C23" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E23" s="15">
         <v>20</v>
@@ -1749,10 +1973,10 @@
     </row>
     <row r="24" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C24" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E24" s="15">
         <v>21</v>
@@ -1760,10 +1984,10 @@
     </row>
     <row r="25" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C25" s="15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E25" s="15">
         <v>22</v>
@@ -1771,10 +1995,10 @@
     </row>
     <row r="26" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C26" s="15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E26" s="15">
         <v>23</v>
@@ -1782,10 +2006,10 @@
     </row>
     <row r="27" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C27" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E27" s="15">
         <v>24</v>
@@ -1793,10 +2017,10 @@
     </row>
     <row r="28" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C28" s="15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E28" s="15">
         <v>25</v>
@@ -1804,10 +2028,10 @@
     </row>
     <row r="29" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C29" s="15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E29" s="15">
         <v>26</v>
@@ -1815,10 +2039,10 @@
     </row>
     <row r="30" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C30" s="15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E30" s="15">
         <v>27</v>
@@ -1826,10 +2050,10 @@
     </row>
     <row r="31" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C31" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E31" s="15">
         <v>28</v>
@@ -1837,10 +2061,10 @@
     </row>
     <row r="32" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C32" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E32" s="15">
         <v>29</v>
@@ -1848,10 +2072,10 @@
     </row>
     <row r="33" spans="3:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C33" s="15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E33" s="15">
         <v>30</v>
@@ -1859,10 +2083,10 @@
     </row>
     <row r="34" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C34" s="15" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="E34" s="15">
         <v>31</v>
@@ -1870,10 +2094,10 @@
     </row>
     <row r="35" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C35" s="15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="E35" s="15">
         <v>32</v>
@@ -1881,10 +2105,10 @@
     </row>
     <row r="36" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C36" s="15" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E36" s="15">
         <v>33</v>
@@ -1892,10 +2116,10 @@
     </row>
     <row r="37" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C37" s="15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E37" s="15">
         <v>34</v>
@@ -1903,10 +2127,10 @@
     </row>
     <row r="38" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C38" s="15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E38" s="15">
         <v>35</v>
@@ -1914,17 +2138,17 @@
     </row>
     <row r="39" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C39" s="23" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D39" s="24"/>
       <c r="E39" s="25"/>
     </row>
-    <row r="40" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="3:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C40" s="7" t="s">
-        <v>91</v>
+        <v>286</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>70</v>
+        <v>285</v>
       </c>
       <c r="E40" s="7">
         <v>36</v>
@@ -1932,10 +2156,10 @@
     </row>
     <row r="41" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C41" s="8" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E41" s="8">
         <v>37</v>
@@ -1943,10 +2167,10 @@
     </row>
     <row r="42" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C42" s="8" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E42" s="8">
         <v>38</v>
@@ -1954,10 +2178,10 @@
     </row>
     <row r="43" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C43" s="8" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E43" s="8">
         <v>39</v>
@@ -1965,21 +2189,21 @@
     </row>
     <row r="44" spans="3:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C44" s="8" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="E44" s="8">
         <v>40</v>
       </c>
     </row>
-    <row r="45" spans="3:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C45" s="8" t="s">
-        <v>96</v>
+        <v>288</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>73</v>
+        <v>287</v>
       </c>
       <c r="E45" s="8">
         <v>41</v>
@@ -1987,10 +2211,10 @@
     </row>
     <row r="46" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C46" s="8" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E46" s="8">
         <v>42</v>
@@ -1998,10 +2222,10 @@
     </row>
     <row r="47" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C47" s="8" t="s">
-        <v>98</v>
+        <v>290</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>75</v>
+        <v>289</v>
       </c>
       <c r="E47" s="8">
         <v>43</v>
@@ -2009,10 +2233,10 @@
     </row>
     <row r="48" spans="3:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C48" s="8" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E48" s="8">
         <v>44</v>
@@ -2020,10 +2244,10 @@
     </row>
     <row r="49" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C49" s="8" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E49" s="8">
         <v>45</v>
@@ -2031,10 +2255,10 @@
     </row>
     <row r="50" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C50" s="8" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E50" s="8">
         <v>46</v>
@@ -2042,32 +2266,32 @@
     </row>
     <row r="51" spans="3:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C51" s="8" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E51" s="8">
         <v>47</v>
       </c>
     </row>
-    <row r="52" spans="3:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="3:5" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C52" s="8" t="s">
-        <v>103</v>
+        <v>292</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>80</v>
+        <v>291</v>
       </c>
       <c r="E52" s="8">
         <v>48</v>
       </c>
     </row>
-    <row r="53" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="3:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C53" s="8" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E53" s="8">
         <v>49</v>
@@ -2075,32 +2299,32 @@
     </row>
     <row r="54" spans="3:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C54" s="8" t="s">
-        <v>105</v>
+        <v>294</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>82</v>
+        <v>293</v>
       </c>
       <c r="E54" s="8">
         <v>50</v>
       </c>
     </row>
-    <row r="55" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="3:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C55" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="D55" s="8" t="s">
-        <v>83</v>
+        <v>296</v>
+      </c>
+      <c r="D55" s="29" t="s">
+        <v>295</v>
       </c>
       <c r="E55" s="8">
         <v>51</v>
       </c>
     </row>
-    <row r="56" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="3:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C56" s="8" t="s">
-        <v>107</v>
+        <v>296</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>84</v>
+        <v>297</v>
       </c>
       <c r="E56" s="8">
         <v>52</v>
@@ -2108,10 +2332,10 @@
     </row>
     <row r="57" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C57" s="8" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E57" s="8">
         <v>53</v>
@@ -2119,10 +2343,10 @@
     </row>
     <row r="58" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C58" s="8" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E58" s="8">
         <v>54</v>
@@ -2130,10 +2354,10 @@
     </row>
     <row r="59" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C59" s="8" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E59" s="8">
         <v>55</v>
@@ -2141,10 +2365,10 @@
     </row>
     <row r="60" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C60" s="8" t="s">
-        <v>109</v>
+        <v>298</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E60" s="8">
         <v>56</v>
@@ -2152,10 +2376,10 @@
     </row>
     <row r="61" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C61" s="8" t="s">
-        <v>110</v>
+        <v>300</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>89</v>
+        <v>299</v>
       </c>
       <c r="E61" s="8">
         <v>57</v>
@@ -2163,10 +2387,10 @@
     </row>
     <row r="62" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C62" s="8" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E62" s="8">
         <v>58</v>
@@ -2174,10 +2398,10 @@
     </row>
     <row r="63" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C63" s="8" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="E63" s="8">
         <v>59</v>
@@ -2185,17 +2409,17 @@
     </row>
     <row r="64" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C64" s="20" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D64" s="20"/>
       <c r="E64" s="20"/>
     </row>
     <row r="65" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C65" s="7" t="s">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>113</v>
+        <v>69</v>
       </c>
       <c r="E65" s="7">
         <v>60</v>
@@ -2203,10 +2427,10 @@
     </row>
     <row r="66" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C66" s="8" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E66" s="8">
         <v>61</v>
@@ -2214,10 +2438,10 @@
     </row>
     <row r="67" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C67" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="D67" s="15" t="s">
-        <v>115</v>
+        <v>127</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>301</v>
       </c>
       <c r="E67" s="8">
         <v>62</v>
@@ -2225,10 +2449,10 @@
     </row>
     <row r="68" spans="3:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C68" s="8" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="D68" s="15" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="E68" s="8">
         <v>63</v>
@@ -2236,10 +2460,10 @@
     </row>
     <row r="69" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C69" s="8" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E69" s="8">
         <v>64</v>
@@ -2248,7 +2472,7 @@
     <row r="70" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C70" s="16"/>
       <c r="D70" s="15" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="E70" s="8">
         <v>65</v>
@@ -2257,7 +2481,7 @@
     <row r="71" spans="3:5" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C71" s="16"/>
       <c r="D71" s="17" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="E71" s="8">
         <v>66</v>
@@ -2265,10 +2489,10 @@
     </row>
     <row r="72" spans="3:5" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C72" s="7" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="E72" s="7">
         <v>67</v>
@@ -2276,10 +2500,10 @@
     </row>
     <row r="73" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C73" s="8" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="E73" s="8">
         <v>68</v>
@@ -2287,10 +2511,10 @@
     </row>
     <row r="74" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C74" s="15" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E74" s="8">
         <v>69</v>
@@ -2298,21 +2522,21 @@
     </row>
     <row r="75" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C75" s="8" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="E75" s="8">
         <v>70</v>
       </c>
     </row>
-    <row r="76" spans="3:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C76" s="8" t="s">
-        <v>141</v>
+        <v>303</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>120</v>
+        <v>302</v>
       </c>
       <c r="E76" s="8">
         <v>71</v>
@@ -2320,10 +2544,10 @@
     </row>
     <row r="77" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C77" s="8" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E77" s="8">
         <v>72</v>
@@ -2331,10 +2555,10 @@
     </row>
     <row r="78" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C78" s="7" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="E78" s="8">
         <v>73</v>
@@ -2342,10 +2566,10 @@
     </row>
     <row r="79" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C79" s="8" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="E79" s="8">
         <v>74</v>
@@ -2354,7 +2578,7 @@
     <row r="80" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C80" s="16"/>
       <c r="D80" s="8" t="s">
-        <v>123</v>
+        <v>304</v>
       </c>
       <c r="E80" s="8">
         <v>75</v>
@@ -2363,7 +2587,7 @@
     <row r="81" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C81" s="16"/>
       <c r="D81" s="8" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E81" s="8">
         <v>76</v>
@@ -2371,10 +2595,10 @@
     </row>
     <row r="82" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C82" s="14" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="E82" s="8">
         <v>77</v>
@@ -2382,10 +2606,10 @@
     </row>
     <row r="83" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C83" s="8" t="s">
-        <v>146</v>
+        <v>100</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>126</v>
+        <v>79</v>
       </c>
       <c r="E83" s="8">
         <v>78</v>
@@ -2393,10 +2617,10 @@
     </row>
     <row r="84" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C84" s="8" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="E84" s="8">
         <v>79</v>
@@ -2404,10 +2628,10 @@
     </row>
     <row r="85" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C85" s="15" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="E85" s="8">
         <v>80</v>
@@ -2415,10 +2639,10 @@
     </row>
     <row r="86" spans="3:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C86" s="15" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="D86" s="8" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E86" s="8">
         <v>81</v>
@@ -2426,10 +2650,10 @@
     </row>
     <row r="87" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C87" s="8" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="D87" s="15" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E87" s="8">
         <v>82</v>
@@ -2437,10 +2661,10 @@
     </row>
     <row r="88" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C88" s="8" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="D88" s="15" t="s">
-        <v>131</v>
+        <v>305</v>
       </c>
       <c r="E88" s="8">
         <v>83</v>
@@ -2448,7 +2672,7 @@
     </row>
     <row r="89" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C89" s="20" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="D89" s="20"/>
       <c r="E89" s="20"/>
@@ -2456,7 +2680,7 @@
     <row r="90" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C90" s="16"/>
       <c r="D90" s="7" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="E90" s="7">
         <v>84</v>
@@ -2465,7 +2689,7 @@
     <row r="91" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C91" s="16"/>
       <c r="D91" s="8" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="E91" s="8">
         <v>85</v>
@@ -2474,7 +2698,7 @@
     <row r="92" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C92" s="16"/>
       <c r="D92" s="8" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="E92" s="8">
         <v>86</v>
@@ -2482,10 +2706,10 @@
     </row>
     <row r="93" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C93" s="7" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="E93" s="8">
         <v>87</v>
@@ -2493,10 +2717,10 @@
     </row>
     <row r="94" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C94" s="8" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="E94" s="8">
         <v>88</v>
@@ -2504,10 +2728,10 @@
     </row>
     <row r="95" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C95" s="7" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="D95" s="8" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="E95" s="8">
         <v>89</v>
@@ -2515,10 +2739,10 @@
     </row>
     <row r="96" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C96" s="8" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E96" s="8">
         <v>90</v>
@@ -2527,7 +2751,7 @@
     <row r="97" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C97" s="9"/>
       <c r="D97" s="8" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="E97" s="8">
         <v>91</v>
@@ -2535,10 +2759,10 @@
     </row>
     <row r="98" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C98" s="7" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="E98" s="8">
         <v>92</v>
@@ -2546,10 +2770,10 @@
     </row>
     <row r="99" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C99" s="8" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="E99" s="8">
         <v>93</v>
@@ -2558,7 +2782,7 @@
     <row r="100" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C100" s="8"/>
       <c r="D100" s="8" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="E100" s="8">
         <v>94</v>
@@ -2566,10 +2790,10 @@
     </row>
     <row r="101" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C101" s="8" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="D101" s="8" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E101" s="8">
         <v>95</v>
@@ -2577,10 +2801,10 @@
     </row>
     <row r="102" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C102" s="8" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="D102" s="8" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="E102" s="8">
         <v>96</v>
@@ -2590,7 +2814,7 @@
     <row r="103" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C103" s="16"/>
       <c r="D103" s="8" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="E103" s="8">
         <v>97</v>
@@ -2600,7 +2824,7 @@
     <row r="104" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C104" s="16"/>
       <c r="D104" s="8" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="E104" s="8">
         <v>98</v>
@@ -2609,10 +2833,10 @@
     </row>
     <row r="105" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C105" s="16" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="D105" s="8" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E105" s="8">
         <v>99</v>
@@ -2622,7 +2846,7 @@
     <row r="106" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C106" s="16"/>
       <c r="D106" s="8" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E106" s="8">
         <v>100</v>
@@ -2632,7 +2856,7 @@
     <row r="107" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C107" s="16"/>
       <c r="D107" s="8" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="E107" s="8">
         <v>101</v>
@@ -2641,10 +2865,10 @@
     </row>
     <row r="108" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C108" s="7" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="D108" s="8" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="E108" s="8">
         <v>102</v>
@@ -2653,10 +2877,10 @@
     </row>
     <row r="109" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C109" s="8" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="D109" s="8" t="s">
-        <v>169</v>
+        <v>86</v>
       </c>
       <c r="E109" s="8">
         <v>103</v>
@@ -2665,10 +2889,10 @@
     </row>
     <row r="110" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C110" s="8" t="s">
-        <v>173</v>
+        <v>103</v>
       </c>
       <c r="D110" s="8" t="s">
-        <v>282</v>
+        <v>81</v>
       </c>
       <c r="E110" s="8">
         <v>104</v>
@@ -2676,9 +2900,11 @@
       <c r="F110" s="2"/>
     </row>
     <row r="111" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C111" s="15"/>
+      <c r="C111" s="15" t="s">
+        <v>103</v>
+      </c>
       <c r="D111" s="8" t="s">
-        <v>170</v>
+        <v>82</v>
       </c>
       <c r="E111" s="8">
         <v>105</v>
@@ -2686,11 +2912,9 @@
       <c r="F111" s="2"/>
     </row>
     <row r="112" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C112" s="15" t="s">
-        <v>174</v>
-      </c>
+      <c r="C112" s="15"/>
       <c r="D112" s="8" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="E112" s="8">
         <v>106</v>
@@ -2699,10 +2923,10 @@
     </row>
     <row r="113" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C113" s="8" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="D113" s="8" t="s">
-        <v>283</v>
+        <v>163</v>
       </c>
       <c r="E113" s="8">
         <v>107</v>
@@ -2711,7 +2935,7 @@
     </row>
     <row r="114" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C114" s="20" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="D114" s="20"/>
       <c r="E114" s="20"/>
@@ -2719,10 +2943,10 @@
     </row>
     <row r="115" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C115" s="7" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="D115" s="7" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="E115" s="8">
         <v>108</v>
@@ -2732,7 +2956,7 @@
     <row r="116" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C116" s="16"/>
       <c r="D116" s="8" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="E116" s="8">
         <v>109</v>
@@ -2741,7 +2965,7 @@
     <row r="117" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C117" s="16"/>
       <c r="D117" s="8" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="E117" s="8">
         <v>110</v>
@@ -2750,27 +2974,29 @@
     <row r="118" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C118" s="16"/>
       <c r="D118" s="8" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="E118" s="8">
         <v>111</v>
       </c>
     </row>
     <row r="119" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C119" s="16"/>
+      <c r="C119" s="16" t="s">
+        <v>306</v>
+      </c>
       <c r="D119" s="8" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="E119" s="8">
         <v>112</v>
       </c>
     </row>
-    <row r="120" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="3:6" ht="34.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C120" s="16" t="s">
-        <v>206</v>
+        <v>101</v>
       </c>
       <c r="D120" s="7" t="s">
-        <v>190</v>
+        <v>307</v>
       </c>
       <c r="E120" s="7">
         <v>113</v>
@@ -2779,7 +3005,7 @@
     <row r="121" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C121" s="16"/>
       <c r="D121" s="15" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="E121" s="8">
         <v>114</v>
@@ -2788,7 +3014,7 @@
     <row r="122" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C122" s="16"/>
       <c r="D122" s="8" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="E122" s="8">
         <v>115</v>
@@ -2796,10 +3022,10 @@
     </row>
     <row r="123" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C123" s="16" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="D123" s="8" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="E123" s="8">
         <v>116</v>
@@ -2808,7 +3034,7 @@
     <row r="124" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C124" s="16"/>
       <c r="D124" s="8" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="E124" s="8">
         <v>117</v>
@@ -2816,10 +3042,10 @@
     </row>
     <row r="125" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C125" s="16" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="D125" s="15" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="E125" s="8">
         <v>118</v>
@@ -2827,10 +3053,10 @@
     </row>
     <row r="126" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C126" s="7" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="D126" s="15" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="E126" s="8">
         <v>119</v>
@@ -2838,21 +3064,21 @@
     </row>
     <row r="127" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C127" s="7" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="D127" s="8" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="E127" s="8">
         <v>120</v>
       </c>
     </row>
-    <row r="128" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="3:6" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C128" s="7" t="s">
-        <v>211</v>
+        <v>93</v>
       </c>
       <c r="D128" s="8" t="s">
-        <v>294</v>
+        <v>72</v>
       </c>
       <c r="E128" s="8">
         <v>121</v>
@@ -2860,10 +3086,10 @@
     </row>
     <row r="129" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C129" s="7" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="D129" s="8" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="E129" s="8">
         <v>122</v>
@@ -2871,10 +3097,10 @@
     </row>
     <row r="130" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C130" s="7" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="D130" s="8" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="E130" s="8">
         <v>123</v>
@@ -2882,10 +3108,10 @@
     </row>
     <row r="131" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C131" s="7" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="D131" s="8" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="E131" s="8">
         <v>124</v>
@@ -2893,10 +3119,10 @@
     </row>
     <row r="132" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C132" s="14" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="D132" s="8" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="E132" s="8">
         <v>125</v>
@@ -2904,10 +3130,10 @@
     </row>
     <row r="133" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C133" s="7" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="D133" s="15" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="E133" s="8">
         <v>126</v>
@@ -2915,10 +3141,10 @@
     </row>
     <row r="134" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C134" s="7" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="D134" s="15" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="E134" s="8">
         <v>127</v>
@@ -2927,16 +3153,16 @@
     <row r="135" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C135" s="16"/>
       <c r="D135" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="E135" s="8">
+        <v>195</v>
+      </c>
+      <c r="E135" s="30">
         <v>128</v>
       </c>
     </row>
     <row r="136" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C136" s="16"/>
       <c r="D136" s="8" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="E136" s="8">
         <v>129</v>
@@ -2944,10 +3170,10 @@
     </row>
     <row r="137" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C137" s="7" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="D137" s="8" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="E137" s="8">
         <v>130</v>
@@ -2955,17 +3181,17 @@
     </row>
     <row r="138" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C138" s="21" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="D138" s="21"/>
       <c r="E138" s="22"/>
     </row>
     <row r="139" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C139" s="16" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="D139" s="7" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="E139" s="7">
         <v>132</v>
@@ -2974,7 +3200,7 @@
     <row r="140" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C140" s="16"/>
       <c r="D140" s="8" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="E140" s="8">
         <v>133</v>
@@ -2982,10 +3208,10 @@
     </row>
     <row r="141" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C141" s="7" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="D141" s="7" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="E141" s="8">
         <v>134</v>
@@ -2993,10 +3219,10 @@
     </row>
     <row r="142" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C142" s="8" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="D142" s="8" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="E142" s="8">
         <v>135</v>
@@ -3004,10 +3230,10 @@
     </row>
     <row r="143" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C143" s="8" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="D143" s="8" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="E143" s="8">
         <v>136</v>
@@ -3015,10 +3241,10 @@
     </row>
     <row r="144" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C144" s="8" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="D144" s="8" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="E144" s="8">
         <v>137</v>
@@ -3026,10 +3252,10 @@
     </row>
     <row r="145" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C145" s="8" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="D145" s="8" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="E145" s="8">
         <v>138</v>
@@ -3037,10 +3263,10 @@
     </row>
     <row r="146" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C146" s="8" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="D146" s="8" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="E146" s="8">
         <v>139</v>
@@ -3048,10 +3274,10 @@
     </row>
     <row r="147" spans="3:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C147" s="8" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="D147" s="8" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="E147" s="8">
         <v>140</v>
@@ -3059,10 +3285,10 @@
     </row>
     <row r="148" spans="3:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C148" s="8" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="D148" s="8" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="E148" s="8">
         <v>141</v>
@@ -3070,10 +3296,10 @@
     </row>
     <row r="149" spans="3:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C149" s="16" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="D149" s="15" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="E149" s="8">
         <v>142</v>
@@ -3081,32 +3307,30 @@
     </row>
     <row r="150" spans="3:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C150" s="9" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="D150" s="8" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E150" s="8">
         <v>143</v>
       </c>
     </row>
     <row r="151" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C151" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="D151" s="8" t="s">
-        <v>226</v>
+      <c r="C151" s="31"/>
+      <c r="D151" s="11" t="s">
+        <v>218</v>
       </c>
       <c r="E151" s="8">
         <v>144</v>
       </c>
     </row>
     <row r="152" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C152" s="3" t="s">
-        <v>244</v>
+      <c r="C152" s="9" t="s">
+        <v>235</v>
       </c>
       <c r="D152" s="8" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="E152" s="8">
         <v>145</v>
@@ -3114,10 +3338,10 @@
     </row>
     <row r="153" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C153" s="3" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="D153" s="8" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="E153" s="8">
         <v>146</v>
@@ -3125,28 +3349,32 @@
     </row>
     <row r="154" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C154" s="3" t="s">
-        <v>177</v>
+        <v>237</v>
       </c>
       <c r="D154" s="18" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="E154" s="8">
         <v>147</v>
       </c>
     </row>
     <row r="155" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C155" s="16"/>
+      <c r="C155" s="3" t="s">
+        <v>169</v>
+      </c>
       <c r="D155" s="11" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="E155" s="8">
         <v>148</v>
       </c>
     </row>
     <row r="156" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C156" s="16"/>
+      <c r="C156" s="16" t="s">
+        <v>165</v>
+      </c>
       <c r="D156" s="16" t="s">
-        <v>267</v>
+        <v>308</v>
       </c>
       <c r="E156" s="8">
         <v>149</v>
@@ -3155,16 +3383,18 @@
     <row r="157" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C157" s="16"/>
       <c r="D157" s="10" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="E157" s="8">
         <v>150</v>
       </c>
     </row>
     <row r="158" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C158" s="16"/>
+      <c r="C158" s="16" t="s">
+        <v>125</v>
+      </c>
       <c r="D158" s="16" t="s">
-        <v>267</v>
+        <v>109</v>
       </c>
       <c r="E158" s="8">
         <v>151</v>
@@ -3172,10 +3402,10 @@
     </row>
     <row r="159" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C159" s="7" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="D159" s="10" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="E159" s="8">
         <v>152</v>
@@ -3184,7 +3414,7 @@
     <row r="160" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C160" s="16"/>
       <c r="D160" s="11" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="E160" s="8">
         <v>153</v>
@@ -3193,7 +3423,7 @@
     <row r="161" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C161" s="16"/>
       <c r="D161" s="11" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="E161" s="8">
         <v>154</v>
@@ -3202,7 +3432,7 @@
     <row r="162" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C162" s="16"/>
       <c r="D162" s="11" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="E162" s="8">
         <v>155</v>
@@ -3210,33 +3440,39 @@
     </row>
     <row r="163" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C163" s="19" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="D163" s="19"/>
       <c r="E163" s="19"/>
     </row>
     <row r="164" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C164" s="16"/>
+      <c r="C164" s="16" t="s">
+        <v>198</v>
+      </c>
       <c r="D164" s="16" t="s">
-        <v>267</v>
+        <v>182</v>
       </c>
       <c r="E164" s="1">
         <v>156</v>
       </c>
     </row>
     <row r="165" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C165" s="16"/>
+      <c r="C165" s="16" t="s">
+        <v>134</v>
+      </c>
       <c r="D165" s="16" t="s">
-        <v>267</v>
+        <v>115</v>
       </c>
       <c r="E165" s="1">
         <v>157</v>
       </c>
     </row>
     <row r="166" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C166" s="16"/>
+      <c r="C166" s="16" t="s">
+        <v>310</v>
+      </c>
       <c r="D166" s="16" t="s">
-        <v>267</v>
+        <v>309</v>
       </c>
       <c r="E166" s="1">
         <v>158</v>
@@ -3245,7 +3481,7 @@
     <row r="167" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C167" s="16"/>
       <c r="D167" s="16" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="E167" s="1">
         <v>159</v>
@@ -3254,61 +3490,73 @@
     <row r="168" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C168" s="16"/>
       <c r="D168" s="16" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="E168" s="1">
         <v>160</v>
       </c>
     </row>
     <row r="169" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C169" s="16"/>
+      <c r="C169" s="16" t="s">
+        <v>312</v>
+      </c>
       <c r="D169" s="16" t="s">
-        <v>267</v>
+        <v>311</v>
       </c>
       <c r="E169" s="1">
         <v>161</v>
       </c>
     </row>
     <row r="170" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C170" s="16"/>
+      <c r="C170" s="3" t="s">
+        <v>199</v>
+      </c>
       <c r="D170" s="16" t="s">
-        <v>267</v>
+        <v>282</v>
       </c>
       <c r="E170" s="1">
         <v>162</v>
       </c>
     </row>
     <row r="171" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C171" s="16"/>
+      <c r="C171" s="16" t="s">
+        <v>314</v>
+      </c>
       <c r="D171" s="16" t="s">
-        <v>267</v>
+        <v>313</v>
       </c>
       <c r="E171" s="1">
         <v>163</v>
       </c>
     </row>
     <row r="172" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C172" s="16"/>
+      <c r="C172" s="16" t="s">
+        <v>139</v>
+      </c>
       <c r="D172" s="16" t="s">
-        <v>267</v>
+        <v>120</v>
       </c>
       <c r="E172" s="1">
         <v>164</v>
       </c>
     </row>
     <row r="173" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C173" s="16"/>
+      <c r="C173" s="16" t="s">
+        <v>167</v>
+      </c>
       <c r="D173" s="16" t="s">
-        <v>267</v>
+        <v>315</v>
       </c>
       <c r="E173" s="1">
         <v>165</v>
       </c>
     </row>
     <row r="174" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C174" s="16"/>
+      <c r="C174" s="16" t="s">
+        <v>203</v>
+      </c>
       <c r="D174" s="3" t="s">
-        <v>203</v>
+        <v>316</v>
       </c>
       <c r="E174" s="1">
         <v>166</v>
@@ -3316,10 +3564,10 @@
     </row>
     <row r="175" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C175" s="3" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="E175" s="1">
         <v>167</v>
@@ -3328,7 +3576,7 @@
     <row r="176" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C176" s="16"/>
       <c r="D176" s="5" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="E176" s="3">
         <v>168</v>
@@ -3337,7 +3585,7 @@
     <row r="177" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C177" s="16"/>
       <c r="D177" s="3" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="E177" s="3">
         <v>169</v>
@@ -3345,10 +3593,10 @@
     </row>
     <row r="178" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C178" s="3" t="s">
-        <v>265</v>
+        <v>318</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>252</v>
+        <v>317</v>
       </c>
       <c r="E178" s="3">
         <v>170</v>
@@ -3357,7 +3605,7 @@
     <row r="179" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C179" s="16"/>
       <c r="D179" s="1" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="E179" s="3">
         <v>171</v>
@@ -3365,10 +3613,10 @@
     </row>
     <row r="180" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C180" s="3" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="E180" s="3">
         <v>172</v>
@@ -3376,10 +3624,10 @@
     </row>
     <row r="181" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C181" s="3" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="E181" s="3">
         <v>173</v>
@@ -3387,10 +3635,10 @@
     </row>
     <row r="182" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C182" s="3" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="E182" s="3">
         <v>174</v>
@@ -3398,10 +3646,10 @@
     </row>
     <row r="183" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C183" s="3" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="E183" s="3">
         <v>175</v>
@@ -3409,10 +3657,10 @@
     </row>
     <row r="184" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C184" s="16" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="E184" s="3">
         <v>176</v>
@@ -3421,7 +3669,7 @@
     <row r="185" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C185" s="16"/>
       <c r="D185" s="1" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E185" s="3">
         <v>177</v>
@@ -3430,25 +3678,168 @@
     <row r="186" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C186" s="16"/>
       <c r="D186" s="1" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="E186" s="3">
         <v>178</v>
       </c>
     </row>
-    <row r="187" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C187" s="16" t="s">
-        <v>177</v>
-      </c>
-      <c r="D187" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="E187" s="3">
+    <row r="187" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C187" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="D187" s="33" t="s">
+        <v>251</v>
+      </c>
+      <c r="E187" s="34">
         <v>179</v>
       </c>
     </row>
+    <row r="188" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C188" s="36" t="s">
+        <v>319</v>
+      </c>
+      <c r="D188" s="36"/>
+      <c r="E188" s="36"/>
+    </row>
+    <row r="189" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C189" s="31"/>
+      <c r="D189" s="31" t="s">
+        <v>320</v>
+      </c>
+      <c r="E189" s="35">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="190" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C190" s="31" t="s">
+        <v>322</v>
+      </c>
+      <c r="D190" s="31" t="s">
+        <v>321</v>
+      </c>
+      <c r="E190" s="35">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="191" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C191" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="D191" s="31" t="s">
+        <v>244</v>
+      </c>
+      <c r="E191" s="35">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="192" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C192" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="D192" s="37" t="s">
+        <v>323</v>
+      </c>
+      <c r="E192" s="35">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="193" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C193" s="31" t="s">
+        <v>326</v>
+      </c>
+      <c r="D193" s="37" t="s">
+        <v>325</v>
+      </c>
+      <c r="E193" s="35">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="194" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C194" s="31" t="s">
+        <v>328</v>
+      </c>
+      <c r="D194" s="31" t="s">
+        <v>327</v>
+      </c>
+      <c r="E194" s="35">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="195" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C195" s="31"/>
+      <c r="D195" s="31" t="s">
+        <v>329</v>
+      </c>
+      <c r="E195" s="35">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="196" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C196" s="31"/>
+      <c r="D196" s="31" t="s">
+        <v>330</v>
+      </c>
+      <c r="E196" s="35">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="197" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C197" s="31"/>
+      <c r="D197" s="31" t="s">
+        <v>331</v>
+      </c>
+      <c r="E197" s="35">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="198" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C198" s="31" t="s">
+        <v>335</v>
+      </c>
+      <c r="D198" s="31" t="s">
+        <v>332</v>
+      </c>
+      <c r="E198" s="35">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="199" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C199" s="31" t="s">
+        <v>335</v>
+      </c>
+      <c r="D199" s="31" t="s">
+        <v>333</v>
+      </c>
+      <c r="E199" s="35">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="200" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C200" s="31" t="s">
+        <v>229</v>
+      </c>
+      <c r="D200" s="31" t="s">
+        <v>213</v>
+      </c>
+      <c r="E200" s="35">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="201" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C201" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="D201" s="31" t="s">
+        <v>334</v>
+      </c>
+      <c r="E201" s="35">
+        <v>192</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
+    <mergeCell ref="C188:E188"/>
     <mergeCell ref="C163:E163"/>
     <mergeCell ref="C114:E114"/>
     <mergeCell ref="C138:E138"/>

--- a/جدول الحضور-1.xlsx
+++ b/جدول الحضور-1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\E.POINT\Desktop\عيد العرش 2026 جهاد\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9372E73-535B-4DDD-8BA3-8B31F64616C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64A10F7C-3514-4588-BD3C-11EB0B9073D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1380" yWindow="660" windowWidth="10752" windowHeight="8964" xr2:uid="{23743375-DD87-4C55-8B35-0449ADC5216E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{23743375-DD87-4C55-8B35-0449ADC5216E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="335">
   <si>
     <t>الصفه</t>
   </si>
@@ -619,9 +619,6 @@
   </si>
   <si>
     <t>الاستاذ كمال عمر الجهاني</t>
-  </si>
-  <si>
-    <t>السيد محمد مصطفى لصفر</t>
   </si>
   <si>
     <t>اللواء علي محمد الديب</t>
@@ -1112,18 +1109,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="14">
@@ -1345,6 +1336,39 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1366,40 +1390,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
   </cellXfs>
@@ -1727,11 +1718,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
     </row>
     <row r="2" spans="3:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C2" s="7" t="s">
@@ -1741,17 +1732,17 @@
         <v>1</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="3" spans="3:5" ht="39" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C3" s="26" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="3" spans="3:5" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="27" t="s">
+      <c r="D3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="28">
+      <c r="E3" s="21">
         <v>1</v>
       </c>
     </row>
@@ -1759,18 +1750,18 @@
       <c r="C4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="28" t="s">
-        <v>283</v>
-      </c>
-      <c r="E4" s="28">
+      <c r="D4" s="21" t="s">
+        <v>282</v>
+      </c>
+      <c r="E4" s="21">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C5" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="D5" s="28" t="s">
+        <v>283</v>
+      </c>
+      <c r="D5" s="21" t="s">
         <v>3</v>
       </c>
       <c r="E5" s="11">
@@ -1781,7 +1772,7 @@
       <c r="C6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="28" t="s">
+      <c r="D6" s="21" t="s">
         <v>5</v>
       </c>
       <c r="E6" s="11">
@@ -1792,18 +1783,18 @@
       <c r="C7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="28" t="s">
+      <c r="D7" s="21" t="s">
         <v>9</v>
       </c>
       <c r="E7" s="11">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="3:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="28" t="s">
+      <c r="D8" s="21" t="s">
         <v>11</v>
       </c>
       <c r="E8" s="11">
@@ -1814,19 +1805,19 @@
       <c r="C9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="28" t="s">
+      <c r="D9" s="21" t="s">
         <v>13</v>
       </c>
       <c r="E9" s="11">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="3:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C10" s="8" t="s">
         <v>14</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E10" s="11">
         <v>8</v>
@@ -1910,11 +1901,11 @@
       </c>
     </row>
     <row r="18" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C18" s="20" t="s">
+      <c r="C18" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="31"/>
     </row>
     <row r="19" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C19" s="14" t="s">
@@ -1932,7 +1923,7 @@
         <v>31</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E20" s="15">
         <v>17</v>
@@ -2070,7 +2061,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="3:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C33" s="15" t="s">
         <v>57</v>
       </c>
@@ -2086,7 +2077,7 @@
         <v>58</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E34" s="15">
         <v>31</v>
@@ -2097,7 +2088,7 @@
         <v>59</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E35" s="15">
         <v>32</v>
@@ -2137,18 +2128,18 @@
       </c>
     </row>
     <row r="39" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C39" s="23" t="s">
+      <c r="C39" s="34" t="s">
         <v>68</v>
       </c>
-      <c r="D39" s="24"/>
-      <c r="E39" s="25"/>
-    </row>
-    <row r="40" spans="3:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D39" s="35"/>
+      <c r="E39" s="36"/>
+    </row>
+    <row r="40" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C40" s="7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E40" s="7">
         <v>36</v>
@@ -2187,12 +2178,12 @@
         <v>39</v>
       </c>
     </row>
-    <row r="44" spans="3:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C44" s="8" t="s">
         <v>92</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E44" s="8">
         <v>40</v>
@@ -2200,10 +2191,10 @@
     </row>
     <row r="45" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C45" s="8" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E45" s="8">
         <v>41</v>
@@ -2222,16 +2213,16 @@
     </row>
     <row r="47" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C47" s="8" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E47" s="8">
         <v>43</v>
       </c>
     </row>
-    <row r="48" spans="3:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C48" s="8" t="s">
         <v>95</v>
       </c>
@@ -2264,7 +2255,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="51" spans="3:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C51" s="8" t="s">
         <v>98</v>
       </c>
@@ -2275,12 +2266,12 @@
         <v>47</v>
       </c>
     </row>
-    <row r="52" spans="3:5" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="3:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C52" s="8" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E52" s="8">
         <v>48</v>
@@ -2299,10 +2290,10 @@
     </row>
     <row r="54" spans="3:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C54" s="8" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E54" s="8">
         <v>50</v>
@@ -2310,10 +2301,10 @@
     </row>
     <row r="55" spans="3:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C55" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="D55" s="29" t="s">
         <v>295</v>
+      </c>
+      <c r="D55" s="22" t="s">
+        <v>294</v>
       </c>
       <c r="E55" s="8">
         <v>51</v>
@@ -2321,10 +2312,10 @@
     </row>
     <row r="56" spans="3:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C56" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="D56" s="8" t="s">
         <v>296</v>
-      </c>
-      <c r="D56" s="8" t="s">
-        <v>297</v>
       </c>
       <c r="E56" s="8">
         <v>52</v>
@@ -2365,7 +2356,7 @@
     </row>
     <row r="60" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C60" s="8" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D60" s="8" t="s">
         <v>85</v>
@@ -2376,10 +2367,10 @@
     </row>
     <row r="61" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C61" s="8" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E61" s="8">
         <v>57</v>
@@ -2401,18 +2392,18 @@
         <v>107</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E63" s="8">
         <v>59</v>
       </c>
     </row>
     <row r="64" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C64" s="20" t="s">
+      <c r="C64" s="31" t="s">
         <v>108</v>
       </c>
-      <c r="D64" s="20"/>
-      <c r="E64" s="20"/>
+      <c r="D64" s="31"/>
+      <c r="E64" s="31"/>
     </row>
     <row r="65" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C65" s="7" t="s">
@@ -2441,13 +2432,13 @@
         <v>127</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E67" s="8">
         <v>62</v>
       </c>
     </row>
-    <row r="68" spans="3:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C68" s="8" t="s">
         <v>128</v>
       </c>
@@ -2472,7 +2463,7 @@
     <row r="70" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C70" s="16"/>
       <c r="D70" s="15" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E70" s="8">
         <v>65</v>
@@ -2481,7 +2472,7 @@
     <row r="71" spans="3:5" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C71" s="16"/>
       <c r="D71" s="17" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E71" s="8">
         <v>66</v>
@@ -2492,7 +2483,7 @@
         <v>130</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E72" s="7">
         <v>67</v>
@@ -2503,7 +2494,7 @@
         <v>131</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E73" s="8">
         <v>68</v>
@@ -2533,10 +2524,10 @@
     </row>
     <row r="76" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C76" s="8" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E76" s="8">
         <v>71</v>
@@ -2558,7 +2549,7 @@
         <v>136</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E78" s="8">
         <v>73</v>
@@ -2578,7 +2569,7 @@
     <row r="80" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C80" s="16"/>
       <c r="D80" s="8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E80" s="8">
         <v>75</v>
@@ -2637,7 +2628,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="86" spans="3:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C86" s="15" t="s">
         <v>142</v>
       </c>
@@ -2664,18 +2655,18 @@
         <v>144</v>
       </c>
       <c r="D88" s="15" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E88" s="8">
         <v>83</v>
       </c>
     </row>
     <row r="89" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C89" s="20" t="s">
+      <c r="C89" s="31" t="s">
         <v>145</v>
       </c>
-      <c r="D89" s="20"/>
-      <c r="E89" s="20"/>
+      <c r="D89" s="31"/>
+      <c r="E89" s="31"/>
     </row>
     <row r="90" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C90" s="16"/>
@@ -2804,7 +2795,7 @@
         <v>172</v>
       </c>
       <c r="D102" s="8" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E102" s="8">
         <v>96</v>
@@ -2814,7 +2805,7 @@
     <row r="103" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C103" s="16"/>
       <c r="D103" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E103" s="8">
         <v>97</v>
@@ -2934,11 +2925,11 @@
       <c r="F113" s="2"/>
     </row>
     <row r="114" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C114" s="20" t="s">
+      <c r="C114" s="31" t="s">
         <v>176</v>
       </c>
-      <c r="D114" s="20"/>
-      <c r="E114" s="20"/>
+      <c r="D114" s="31"/>
+      <c r="E114" s="31"/>
       <c r="F114" s="2"/>
     </row>
     <row r="115" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
@@ -2956,7 +2947,7 @@
     <row r="116" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C116" s="16"/>
       <c r="D116" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E116" s="8">
         <v>109</v>
@@ -2982,7 +2973,7 @@
     </row>
     <row r="119" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C119" s="16" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D119" s="8" t="s">
         <v>181</v>
@@ -2996,7 +2987,7 @@
         <v>101</v>
       </c>
       <c r="D120" s="7" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E120" s="7">
         <v>113</v>
@@ -3022,10 +3013,10 @@
     </row>
     <row r="123" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C123" s="16" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D123" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E123" s="8">
         <v>116</v>
@@ -3042,7 +3033,7 @@
     </row>
     <row r="125" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C125" s="16" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D125" s="15" t="s">
         <v>186</v>
@@ -3053,7 +3044,7 @@
     </row>
     <row r="126" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C126" s="7" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D126" s="15" t="s">
         <v>187</v>
@@ -3064,7 +3055,7 @@
     </row>
     <row r="127" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C127" s="7" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D127" s="8" t="s">
         <v>188</v>
@@ -3073,7 +3064,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="128" spans="3:6" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C128" s="7" t="s">
         <v>93</v>
       </c>
@@ -3097,7 +3088,7 @@
     </row>
     <row r="130" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C130" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D130" s="8" t="s">
         <v>190</v>
@@ -3130,7 +3121,7 @@
     </row>
     <row r="133" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C133" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D133" s="15" t="s">
         <v>193</v>
@@ -3141,7 +3132,7 @@
     </row>
     <row r="134" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C134" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D134" s="15" t="s">
         <v>194</v>
@@ -3153,16 +3144,16 @@
     <row r="135" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C135" s="16"/>
       <c r="D135" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="E135" s="30">
+        <v>258</v>
+      </c>
+      <c r="E135" s="37">
         <v>128</v>
       </c>
     </row>
     <row r="136" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C136" s="16"/>
       <c r="D136" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E136" s="8">
         <v>129</v>
@@ -3170,28 +3161,28 @@
     </row>
     <row r="137" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C137" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D137" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E137" s="8">
         <v>130</v>
       </c>
     </row>
     <row r="138" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C138" s="21" t="s">
-        <v>239</v>
-      </c>
-      <c r="D138" s="21"/>
-      <c r="E138" s="22"/>
+      <c r="C138" s="32" t="s">
+        <v>238</v>
+      </c>
+      <c r="D138" s="32"/>
+      <c r="E138" s="33"/>
     </row>
     <row r="139" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C139" s="16" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D139" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E139" s="7">
         <v>132</v>
@@ -3200,7 +3191,7 @@
     <row r="140" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C140" s="16"/>
       <c r="D140" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E140" s="8">
         <v>133</v>
@@ -3208,10 +3199,10 @@
     </row>
     <row r="141" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C141" s="7" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D141" s="7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E141" s="8">
         <v>134</v>
@@ -3219,10 +3210,10 @@
     </row>
     <row r="142" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C142" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D142" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E142" s="8">
         <v>135</v>
@@ -3230,10 +3221,10 @@
     </row>
     <row r="143" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C143" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D143" s="8" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E143" s="8">
         <v>136</v>
@@ -3241,10 +3232,10 @@
     </row>
     <row r="144" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C144" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D144" s="8" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E144" s="8">
         <v>137</v>
@@ -3252,10 +3243,10 @@
     </row>
     <row r="145" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C145" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D145" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E145" s="8">
         <v>138</v>
@@ -3263,10 +3254,10 @@
     </row>
     <row r="146" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C146" s="8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D146" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E146" s="8">
         <v>139</v>
@@ -3274,10 +3265,10 @@
     </row>
     <row r="147" spans="3:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C147" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D147" s="8" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E147" s="8">
         <v>140</v>
@@ -3285,10 +3276,10 @@
     </row>
     <row r="148" spans="3:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C148" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D148" s="8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E148" s="8">
         <v>141</v>
@@ -3296,10 +3287,10 @@
     </row>
     <row r="149" spans="3:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C149" s="16" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D149" s="15" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E149" s="8">
         <v>142</v>
@@ -3307,19 +3298,19 @@
     </row>
     <row r="150" spans="3:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C150" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D150" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E150" s="8">
         <v>143</v>
       </c>
     </row>
     <row r="151" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C151" s="31"/>
+      <c r="C151" s="23"/>
       <c r="D151" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E151" s="8">
         <v>144</v>
@@ -3327,10 +3318,10 @@
     </row>
     <row r="152" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C152" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D152" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E152" s="8">
         <v>145</v>
@@ -3338,10 +3329,10 @@
     </row>
     <row r="153" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C153" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D153" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E153" s="8">
         <v>146</v>
@@ -3349,10 +3340,10 @@
     </row>
     <row r="154" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C154" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D154" s="18" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E154" s="8">
         <v>147</v>
@@ -3363,7 +3354,7 @@
         <v>169</v>
       </c>
       <c r="D155" s="11" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E155" s="8">
         <v>148</v>
@@ -3374,7 +3365,7 @@
         <v>165</v>
       </c>
       <c r="D156" s="16" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E156" s="8">
         <v>149</v>
@@ -3383,7 +3374,7 @@
     <row r="157" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C157" s="16"/>
       <c r="D157" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E157" s="8">
         <v>150</v>
@@ -3402,10 +3393,10 @@
     </row>
     <row r="159" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C159" s="7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D159" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E159" s="8">
         <v>152</v>
@@ -3414,7 +3405,7 @@
     <row r="160" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C160" s="16"/>
       <c r="D160" s="11" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E160" s="8">
         <v>153</v>
@@ -3423,7 +3414,7 @@
     <row r="161" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C161" s="16"/>
       <c r="D161" s="11" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E161" s="8">
         <v>154</v>
@@ -3432,22 +3423,22 @@
     <row r="162" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C162" s="16"/>
       <c r="D162" s="11" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E162" s="8">
         <v>155</v>
       </c>
     </row>
     <row r="163" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C163" s="19" t="s">
-        <v>241</v>
-      </c>
-      <c r="D163" s="19"/>
-      <c r="E163" s="19"/>
+      <c r="C163" s="30" t="s">
+        <v>240</v>
+      </c>
+      <c r="D163" s="30"/>
+      <c r="E163" s="30"/>
     </row>
     <row r="164" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C164" s="16" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D164" s="16" t="s">
         <v>182</v>
@@ -3469,10 +3460,10 @@
     </row>
     <row r="166" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C166" s="16" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D166" s="16" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E166" s="1">
         <v>158</v>
@@ -3481,7 +3472,7 @@
     <row r="167" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C167" s="16"/>
       <c r="D167" s="16" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E167" s="1">
         <v>159</v>
@@ -3490,7 +3481,7 @@
     <row r="168" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C168" s="16"/>
       <c r="D168" s="16" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E168" s="1">
         <v>160</v>
@@ -3498,10 +3489,10 @@
     </row>
     <row r="169" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C169" s="16" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D169" s="16" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E169" s="1">
         <v>161</v>
@@ -3509,10 +3500,10 @@
     </row>
     <row r="170" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C170" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D170" s="16" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E170" s="1">
         <v>162</v>
@@ -3520,10 +3511,10 @@
     </row>
     <row r="171" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C171" s="16" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D171" s="16" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E171" s="1">
         <v>163</v>
@@ -3545,7 +3536,7 @@
         <v>167</v>
       </c>
       <c r="D173" s="16" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E173" s="1">
         <v>165</v>
@@ -3553,10 +3544,10 @@
     </row>
     <row r="174" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C174" s="16" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E174" s="1">
         <v>166</v>
@@ -3564,10 +3555,10 @@
     </row>
     <row r="175" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C175" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E175" s="1">
         <v>167</v>
@@ -3576,7 +3567,7 @@
     <row r="176" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C176" s="16"/>
       <c r="D176" s="5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E176" s="3">
         <v>168</v>
@@ -3585,7 +3576,7 @@
     <row r="177" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C177" s="16"/>
       <c r="D177" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E177" s="3">
         <v>169</v>
@@ -3593,10 +3584,10 @@
     </row>
     <row r="178" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C178" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E178" s="3">
         <v>170</v>
@@ -3605,7 +3596,7 @@
     <row r="179" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C179" s="16"/>
       <c r="D179" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E179" s="3">
         <v>171</v>
@@ -3613,10 +3604,10 @@
     </row>
     <row r="180" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C180" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E180" s="3">
         <v>172</v>
@@ -3624,10 +3615,10 @@
     </row>
     <row r="181" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C181" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E181" s="3">
         <v>173</v>
@@ -3638,7 +3629,7 @@
         <v>169</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E182" s="3">
         <v>174</v>
@@ -3646,10 +3637,10 @@
     </row>
     <row r="183" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C183" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E183" s="3">
         <v>175</v>
@@ -3657,10 +3648,10 @@
     </row>
     <row r="184" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C184" s="16" t="s">
+        <v>251</v>
+      </c>
+      <c r="D184" s="1" t="s">
         <v>252</v>
-      </c>
-      <c r="D184" s="1" t="s">
-        <v>253</v>
       </c>
       <c r="E184" s="3">
         <v>176</v>
@@ -3669,7 +3660,7 @@
     <row r="185" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C185" s="16"/>
       <c r="D185" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E185" s="3">
         <v>177</v>
@@ -3678,176 +3669,176 @@
     <row r="186" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C186" s="16"/>
       <c r="D186" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E186" s="3">
         <v>178</v>
       </c>
     </row>
     <row r="187" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C187" s="32" t="s">
+      <c r="C187" s="24" t="s">
         <v>169</v>
       </c>
-      <c r="D187" s="33" t="s">
-        <v>251</v>
-      </c>
-      <c r="E187" s="34">
+      <c r="D187" s="25" t="s">
+        <v>250</v>
+      </c>
+      <c r="E187" s="26">
         <v>179</v>
       </c>
     </row>
     <row r="188" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C188" s="36" t="s">
+      <c r="C188" s="29" t="s">
+        <v>318</v>
+      </c>
+      <c r="D188" s="29"/>
+      <c r="E188" s="29"/>
+    </row>
+    <row r="189" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C189" s="23"/>
+      <c r="D189" s="23" t="s">
         <v>319</v>
       </c>
-      <c r="D188" s="36"/>
-      <c r="E188" s="36"/>
-    </row>
-    <row r="189" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C189" s="31"/>
-      <c r="D189" s="31" t="s">
+      <c r="E189" s="27">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="190" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C190" s="23" t="s">
+        <v>321</v>
+      </c>
+      <c r="D190" s="23" t="s">
         <v>320</v>
       </c>
-      <c r="E189" s="35">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="190" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C190" s="31" t="s">
-        <v>322</v>
-      </c>
-      <c r="D190" s="31" t="s">
-        <v>321</v>
-      </c>
-      <c r="E190" s="35">
+      <c r="E190" s="27">
         <v>181</v>
       </c>
     </row>
     <row r="191" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C191" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="D191" s="31" t="s">
-        <v>244</v>
-      </c>
-      <c r="E191" s="35">
+        <v>256</v>
+      </c>
+      <c r="D191" s="23" t="s">
+        <v>243</v>
+      </c>
+      <c r="E191" s="27">
         <v>182</v>
       </c>
     </row>
     <row r="192" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C192" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="D192" s="28" t="s">
+        <v>322</v>
+      </c>
+      <c r="E192" s="27">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="193" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C193" s="23" t="s">
+        <v>325</v>
+      </c>
+      <c r="D193" s="28" t="s">
         <v>324</v>
       </c>
-      <c r="D192" s="37" t="s">
-        <v>323</v>
-      </c>
-      <c r="E192" s="35">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="193" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C193" s="31" t="s">
+      <c r="E193" s="27">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="194" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C194" s="23" t="s">
+        <v>327</v>
+      </c>
+      <c r="D194" s="23" t="s">
         <v>326</v>
       </c>
-      <c r="D193" s="37" t="s">
-        <v>325</v>
-      </c>
-      <c r="E193" s="35">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="194" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C194" s="31" t="s">
+      <c r="E194" s="27">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="195" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C195" s="23"/>
+      <c r="D195" s="23" t="s">
         <v>328</v>
       </c>
-      <c r="D194" s="31" t="s">
-        <v>327</v>
-      </c>
-      <c r="E194" s="35">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="195" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C195" s="31"/>
-      <c r="D195" s="31" t="s">
+      <c r="E195" s="27">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="196" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C196" s="23"/>
+      <c r="D196" s="23" t="s">
         <v>329</v>
       </c>
-      <c r="E195" s="35">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="196" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C196" s="31"/>
-      <c r="D196" s="31" t="s">
+      <c r="E196" s="27">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="197" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C197" s="23"/>
+      <c r="D197" s="23" t="s">
         <v>330</v>
       </c>
-      <c r="E196" s="35">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="197" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C197" s="31"/>
-      <c r="D197" s="31" t="s">
+      <c r="E197" s="27">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="198" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C198" s="23" t="s">
+        <v>334</v>
+      </c>
+      <c r="D198" s="23" t="s">
         <v>331</v>
       </c>
-      <c r="E197" s="35">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="198" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C198" s="31" t="s">
-        <v>335</v>
-      </c>
-      <c r="D198" s="31" t="s">
+      <c r="E198" s="27">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="199" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C199" s="23" t="s">
+        <v>334</v>
+      </c>
+      <c r="D199" s="23" t="s">
         <v>332</v>
       </c>
-      <c r="E198" s="35">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="199" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C199" s="31" t="s">
-        <v>335</v>
-      </c>
-      <c r="D199" s="31" t="s">
+      <c r="E199" s="27">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="200" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C200" s="23" t="s">
+        <v>228</v>
+      </c>
+      <c r="D200" s="23" t="s">
+        <v>212</v>
+      </c>
+      <c r="E200" s="27">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="201" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C201" s="23" t="s">
+        <v>131</v>
+      </c>
+      <c r="D201" s="23" t="s">
         <v>333</v>
       </c>
-      <c r="E199" s="35">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="200" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C200" s="31" t="s">
-        <v>229</v>
-      </c>
-      <c r="D200" s="31" t="s">
-        <v>213</v>
-      </c>
-      <c r="E200" s="35">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="201" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C201" s="31" t="s">
-        <v>131</v>
-      </c>
-      <c r="D201" s="31" t="s">
-        <v>334</v>
-      </c>
-      <c r="E201" s="35">
+      <c r="E201" s="27">
         <v>192</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="C64:E64"/>
+    <mergeCell ref="C89:E89"/>
     <mergeCell ref="C188:E188"/>
     <mergeCell ref="C163:E163"/>
     <mergeCell ref="C114:E114"/>
     <mergeCell ref="C138:E138"/>
     <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="C39:E39"/>
-    <mergeCell ref="C64:E64"/>
-    <mergeCell ref="C89:E89"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/جدول الحضور-1.xlsx
+++ b/جدول الحضور-1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\E.POINT\Desktop\عيد العرش 2026 جهاد\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64A10F7C-3514-4588-BD3C-11EB0B9073D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33E6C249-257A-4F3B-908C-3540BEAD5C9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{23743375-DD87-4C55-8B35-0449ADC5216E}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="335">
   <si>
     <t>الصفه</t>
   </si>
@@ -1045,7 +1045,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1063,47 +1063,6 @@
     <font>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="15"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1117,140 +1076,11 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -1269,129 +1099,36 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1707,2125 +1444,2197 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18A94353-2125-49E6-91ED-D3B1232B2558}">
-  <dimension ref="A1:F201"/>
+  <dimension ref="A1:F209"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.88671875" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8.88671875" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="66.109375" style="6" customWidth="1"/>
-    <col min="4" max="4" width="41" style="6" customWidth="1"/>
-    <col min="5" max="5" width="9.88671875" style="4" customWidth="1"/>
+    <col min="3" max="3" width="66.109375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="41" style="3" customWidth="1"/>
+    <col min="5" max="5" width="9.88671875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C1" s="31" t="s">
+    <row r="1" spans="3:5" ht="18" x14ac:dyDescent="0.35">
+      <c r="C1" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-    </row>
-    <row r="2" spans="3:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C2" s="7" t="s">
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+    </row>
+    <row r="2" spans="3:5" ht="36" x14ac:dyDescent="0.3">
+      <c r="C2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="6" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="3" spans="3:5" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C3" s="19" t="s">
+    <row r="3" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="D3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="21">
+      <c r="E3" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C4" s="3" t="s">
+    <row r="4" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C4" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="D4" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C5" s="3" t="s">
+    <row r="5" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C5" s="6" t="s">
         <v>283</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="6">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C6" s="3" t="s">
+    <row r="6" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C6" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="D6" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="6">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C7" s="3" t="s">
+    <row r="7" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C7" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="21" t="s">
+      <c r="D7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="6">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C8" s="3" t="s">
+    <row r="8" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C8" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="6">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C9" s="3" t="s">
+    <row r="9" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C9" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="21" t="s">
+      <c r="D9" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="6">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C10" s="8" t="s">
+    <row r="10" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C10" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="6">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C11" s="8" t="s">
+    <row r="11" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C11" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="6">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C12" s="8" t="s">
+    <row r="12" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C12" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E12" s="11">
+      <c r="E12" s="6">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C13" s="8" t="s">
+    <row r="13" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C13" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E13" s="11">
+      <c r="E13" s="6">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C14" s="8" t="s">
+    <row r="14" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C14" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="11">
+      <c r="E14" s="6">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C15" s="8" t="s">
+    <row r="15" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C15" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E15" s="11">
+      <c r="E15" s="6">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C16" s="8" t="s">
+    <row r="16" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C16" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E16" s="11">
+      <c r="E16" s="6">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C17" s="12" t="s">
+    <row r="17" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C17" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D17" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E17" s="13">
+      <c r="E17" s="6">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C18" s="31" t="s">
+    <row r="18" spans="3:5" ht="18" x14ac:dyDescent="0.35">
+      <c r="C18" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D18" s="31"/>
-      <c r="E18" s="31"/>
-    </row>
-    <row r="19" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C19" s="14" t="s">
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+    </row>
+    <row r="19" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C19" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D19" s="14" t="s">
+      <c r="D19" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E19" s="15">
+      <c r="E19" s="7">
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C20" s="15" t="s">
+    <row r="20" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C20" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="D20" s="15" t="s">
+      <c r="D20" s="7" t="s">
         <v>261</v>
       </c>
-      <c r="E20" s="15">
+      <c r="E20" s="7">
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C21" s="15" t="s">
+    <row r="21" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C21" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D21" s="15" t="s">
+      <c r="D21" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E21" s="15">
+      <c r="E21" s="7">
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C22" s="15" t="s">
+    <row r="22" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C22" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D22" s="15" t="s">
+      <c r="D22" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E22" s="15">
+      <c r="E22" s="7">
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C23" s="15" t="s">
+    <row r="23" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C23" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D23" s="15" t="s">
+      <c r="D23" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="E23" s="15">
+      <c r="E23" s="7">
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C24" s="15" t="s">
+    <row r="24" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C24" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D24" s="15" t="s">
+      <c r="D24" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="E24" s="15">
+      <c r="E24" s="7">
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C25" s="15" t="s">
+    <row r="25" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C25" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D25" s="15" t="s">
+      <c r="D25" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E25" s="15">
+      <c r="E25" s="7">
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C26" s="15" t="s">
+    <row r="26" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C26" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D26" s="15" t="s">
+      <c r="D26" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E26" s="15">
+      <c r="E26" s="7">
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C27" s="15" t="s">
+    <row r="27" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C27" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="D27" s="15" t="s">
+      <c r="D27" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="E27" s="15">
+      <c r="E27" s="7">
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C28" s="15" t="s">
+    <row r="28" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C28" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="D28" s="15" t="s">
+      <c r="D28" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="E28" s="15">
+      <c r="E28" s="7">
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C29" s="15" t="s">
+    <row r="29" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C29" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D29" s="15" t="s">
+      <c r="D29" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="E29" s="15">
+      <c r="E29" s="7">
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C30" s="15" t="s">
+    <row r="30" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C30" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D30" s="15" t="s">
+      <c r="D30" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="E30" s="15">
+      <c r="E30" s="7">
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C31" s="15" t="s">
+    <row r="31" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C31" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D31" s="15" t="s">
+      <c r="D31" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E31" s="15">
+      <c r="E31" s="7">
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C32" s="15" t="s">
+    <row r="32" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C32" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="D32" s="15" t="s">
+      <c r="D32" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="E32" s="15">
+      <c r="E32" s="7">
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C33" s="15" t="s">
+    <row r="33" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C33" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="D33" s="15" t="s">
+      <c r="D33" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="E33" s="15">
+      <c r="E33" s="7">
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C34" s="15" t="s">
+    <row r="34" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C34" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D34" s="15" t="s">
+      <c r="D34" s="7" t="s">
         <v>262</v>
       </c>
-      <c r="E34" s="15">
+      <c r="E34" s="7">
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C35" s="15" t="s">
+    <row r="35" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C35" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="D35" s="15" t="s">
+      <c r="D35" s="7" t="s">
         <v>263</v>
       </c>
-      <c r="E35" s="15">
+      <c r="E35" s="7">
         <v>32</v>
       </c>
     </row>
-    <row r="36" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C36" s="15" t="s">
+    <row r="36" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C36" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="D36" s="15" t="s">
+      <c r="D36" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E36" s="15">
+      <c r="E36" s="7">
         <v>33</v>
       </c>
     </row>
-    <row r="37" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C37" s="15" t="s">
+    <row r="37" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C37" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="D37" s="15" t="s">
+      <c r="D37" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="E37" s="15">
+      <c r="E37" s="7">
         <v>34</v>
       </c>
     </row>
-    <row r="38" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C38" s="15" t="s">
+    <row r="38" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C38" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D38" s="15" t="s">
+      <c r="D38" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E38" s="15">
+      <c r="E38" s="7">
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C39" s="34" t="s">
+    <row r="39" spans="3:5" ht="18" x14ac:dyDescent="0.35">
+      <c r="C39" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="D39" s="35"/>
-      <c r="E39" s="36"/>
-    </row>
-    <row r="40" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C40" s="7" t="s">
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+    </row>
+    <row r="40" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C40" s="6" t="s">
         <v>285</v>
       </c>
-      <c r="D40" s="7" t="s">
+      <c r="D40" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="E40" s="7">
+      <c r="E40" s="6">
         <v>36</v>
       </c>
     </row>
-    <row r="41" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C41" s="8" t="s">
+    <row r="41" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C41" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D41" s="8" t="s">
+      <c r="D41" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="E41" s="8">
+      <c r="E41" s="6">
         <v>37</v>
       </c>
     </row>
-    <row r="42" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C42" s="8" t="s">
+    <row r="42" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C42" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="D42" s="8" t="s">
+      <c r="D42" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E42" s="8">
+      <c r="E42" s="6">
         <v>38</v>
       </c>
     </row>
-    <row r="43" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C43" s="8" t="s">
+    <row r="43" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C43" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D43" s="8" t="s">
+      <c r="D43" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="E43" s="8">
+      <c r="E43" s="6">
         <v>39</v>
       </c>
     </row>
-    <row r="44" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C44" s="8" t="s">
+    <row r="44" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C44" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D44" s="8" t="s">
+      <c r="D44" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="E44" s="8">
+      <c r="E44" s="6">
         <v>40</v>
       </c>
     </row>
-    <row r="45" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C45" s="8" t="s">
+    <row r="45" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C45" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="D45" s="8" t="s">
+      <c r="D45" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="E45" s="8">
+      <c r="E45" s="6">
         <v>41</v>
       </c>
     </row>
-    <row r="46" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C46" s="8" t="s">
+    <row r="46" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C46" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="D46" s="8" t="s">
+      <c r="D46" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="E46" s="8">
+      <c r="E46" s="6">
         <v>42</v>
       </c>
     </row>
-    <row r="47" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C47" s="8" t="s">
+    <row r="47" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C47" s="6" t="s">
         <v>289</v>
       </c>
-      <c r="D47" s="8" t="s">
+      <c r="D47" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="E47" s="8">
+      <c r="E47" s="6">
         <v>43</v>
       </c>
     </row>
-    <row r="48" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C48" s="8" t="s">
+    <row r="48" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C48" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="D48" s="8" t="s">
+      <c r="D48" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="E48" s="8">
+      <c r="E48" s="6">
         <v>44</v>
       </c>
     </row>
-    <row r="49" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C49" s="8" t="s">
+    <row r="49" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C49" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="D49" s="8" t="s">
+      <c r="D49" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="E49" s="8">
+      <c r="E49" s="6">
         <v>45</v>
       </c>
     </row>
-    <row r="50" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C50" s="8" t="s">
+    <row r="50" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C50" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="D50" s="8" t="s">
+      <c r="D50" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="E50" s="8">
+      <c r="E50" s="6">
         <v>46</v>
       </c>
     </row>
-    <row r="51" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C51" s="8" t="s">
+    <row r="51" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C51" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="D51" s="8" t="s">
+      <c r="D51" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="E51" s="8">
+      <c r="E51" s="6">
         <v>47</v>
       </c>
     </row>
-    <row r="52" spans="3:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C52" s="8" t="s">
+    <row r="52" spans="3:5" ht="36" x14ac:dyDescent="0.3">
+      <c r="C52" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="D52" s="8" t="s">
+      <c r="D52" s="6" t="s">
         <v>290</v>
       </c>
-      <c r="E52" s="8">
+      <c r="E52" s="6">
         <v>48</v>
       </c>
     </row>
-    <row r="53" spans="3:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C53" s="8" t="s">
+    <row r="53" spans="3:5" ht="36" x14ac:dyDescent="0.3">
+      <c r="C53" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="D53" s="8" t="s">
+      <c r="D53" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="E53" s="8">
+      <c r="E53" s="6">
         <v>49</v>
       </c>
     </row>
-    <row r="54" spans="3:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C54" s="8" t="s">
+    <row r="54" spans="3:5" ht="36" x14ac:dyDescent="0.3">
+      <c r="C54" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="D54" s="8" t="s">
+      <c r="D54" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="E54" s="8">
+      <c r="E54" s="6">
         <v>50</v>
       </c>
     </row>
-    <row r="55" spans="3:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C55" s="8" t="s">
+    <row r="55" spans="3:5" ht="36" x14ac:dyDescent="0.3">
+      <c r="C55" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="D55" s="22" t="s">
+      <c r="D55" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="E55" s="8">
+      <c r="E55" s="6">
         <v>51</v>
       </c>
     </row>
-    <row r="56" spans="3:5" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C56" s="8" t="s">
+    <row r="56" spans="3:5" ht="36" x14ac:dyDescent="0.3">
+      <c r="C56" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="D56" s="8" t="s">
+      <c r="D56" s="6" t="s">
         <v>296</v>
       </c>
-      <c r="E56" s="8">
+      <c r="E56" s="6">
         <v>52</v>
       </c>
     </row>
-    <row r="57" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C57" s="8" t="s">
+    <row r="57" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C57" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="D57" s="8" t="s">
+      <c r="D57" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="E57" s="8">
+      <c r="E57" s="6">
         <v>53</v>
       </c>
     </row>
-    <row r="58" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C58" s="8" t="s">
+    <row r="58" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C58" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="D58" s="8" t="s">
+      <c r="D58" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="E58" s="8">
+      <c r="E58" s="6">
         <v>54</v>
       </c>
     </row>
-    <row r="59" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C59" s="8" t="s">
+    <row r="59" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C59" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="D59" s="8" t="s">
+      <c r="D59" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="E59" s="8">
+      <c r="E59" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="60" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C60" s="8" t="s">
+    <row r="60" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C60" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="D60" s="8" t="s">
+      <c r="D60" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="E60" s="8">
+      <c r="E60" s="6">
         <v>56</v>
       </c>
     </row>
-    <row r="61" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C61" s="8" t="s">
+    <row r="61" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C61" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="D61" s="8" t="s">
+      <c r="D61" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="E61" s="8">
+      <c r="E61" s="6">
         <v>57</v>
       </c>
     </row>
-    <row r="62" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C62" s="8" t="s">
+    <row r="62" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C62" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="D62" s="8" t="s">
+      <c r="D62" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="E62" s="8">
+      <c r="E62" s="6">
         <v>58</v>
       </c>
     </row>
-    <row r="63" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C63" s="8" t="s">
+    <row r="63" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C63" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="D63" s="8" t="s">
+      <c r="D63" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="E63" s="8">
+      <c r="E63" s="6">
         <v>59</v>
       </c>
     </row>
-    <row r="64" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C64" s="31" t="s">
+    <row r="64" spans="3:5" ht="18" x14ac:dyDescent="0.35">
+      <c r="C64" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="D64" s="31"/>
-      <c r="E64" s="31"/>
-    </row>
-    <row r="65" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C65" s="7" t="s">
+      <c r="D64" s="5"/>
+      <c r="E64" s="5"/>
+    </row>
+    <row r="65" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C65" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="D65" s="7" t="s">
+      <c r="D65" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E65" s="7">
+      <c r="E65" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="66" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C66" s="8" t="s">
+    <row r="66" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C66" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="D66" s="8" t="s">
+      <c r="D66" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="E66" s="8">
+      <c r="E66" s="6">
         <v>61</v>
       </c>
     </row>
-    <row r="67" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C67" s="8" t="s">
+    <row r="67" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C67" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="D67" s="8" t="s">
+      <c r="D67" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="E67" s="8">
+      <c r="E67" s="6">
         <v>62</v>
       </c>
     </row>
-    <row r="68" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C68" s="8" t="s">
+    <row r="68" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C68" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="D68" s="15" t="s">
+      <c r="D68" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="E68" s="8">
+      <c r="E68" s="6">
         <v>63</v>
       </c>
     </row>
-    <row r="69" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C69" s="8" t="s">
+    <row r="69" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C69" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="D69" s="8" t="s">
+      <c r="D69" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="E69" s="8">
+      <c r="E69" s="6">
         <v>64</v>
       </c>
     </row>
-    <row r="70" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C70" s="16"/>
-      <c r="D70" s="15" t="s">
+    <row r="70" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C70" s="4"/>
+      <c r="D70" s="7" t="s">
         <v>266</v>
       </c>
-      <c r="E70" s="8">
+      <c r="E70" s="6">
         <v>65</v>
       </c>
     </row>
-    <row r="71" spans="3:5" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C71" s="16"/>
-      <c r="D71" s="17" t="s">
+    <row r="71" spans="3:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C71" s="4"/>
+      <c r="D71" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="E71" s="8">
+      <c r="E71" s="6">
         <v>66</v>
       </c>
     </row>
-    <row r="72" spans="3:5" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C72" s="7" t="s">
+    <row r="72" spans="3:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C72" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="D72" s="8" t="s">
+      <c r="D72" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="E72" s="7">
+      <c r="E72" s="6">
         <v>67</v>
       </c>
     </row>
-    <row r="73" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C73" s="8" t="s">
+    <row r="73" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C73" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="D73" s="8" t="s">
+      <c r="D73" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="E73" s="8">
+      <c r="E73" s="6">
         <v>68</v>
       </c>
     </row>
-    <row r="74" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C74" s="15" t="s">
+    <row r="74" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C74" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="D74" s="8" t="s">
+      <c r="D74" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="E74" s="8">
+      <c r="E74" s="6">
         <v>69</v>
       </c>
     </row>
-    <row r="75" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C75" s="8" t="s">
+    <row r="75" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C75" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="D75" s="8" t="s">
+      <c r="D75" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="E75" s="8">
+      <c r="E75" s="6">
         <v>70</v>
       </c>
     </row>
-    <row r="76" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C76" s="8" t="s">
+    <row r="76" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C76" s="6" t="s">
         <v>302</v>
       </c>
-      <c r="D76" s="8" t="s">
+      <c r="D76" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="E76" s="8">
+      <c r="E76" s="6">
         <v>71</v>
       </c>
     </row>
-    <row r="77" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C77" s="8" t="s">
+    <row r="77" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C77" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="D77" s="8" t="s">
+      <c r="D77" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E77" s="8">
+      <c r="E77" s="6">
         <v>72</v>
       </c>
     </row>
-    <row r="78" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C78" s="7" t="s">
+    <row r="78" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C78" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="D78" s="8" t="s">
+      <c r="D78" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="E78" s="8">
+      <c r="E78" s="6">
         <v>73</v>
       </c>
     </row>
-    <row r="79" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C79" s="8" t="s">
+    <row r="79" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C79" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="D79" s="8" t="s">
+      <c r="D79" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="E79" s="8">
+      <c r="E79" s="6">
         <v>74</v>
       </c>
     </row>
-    <row r="80" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C80" s="16"/>
-      <c r="D80" s="8" t="s">
+    <row r="80" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C80" s="4"/>
+      <c r="D80" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="E80" s="8">
+      <c r="E80" s="6">
         <v>75</v>
       </c>
     </row>
-    <row r="81" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C81" s="16"/>
-      <c r="D81" s="8" t="s">
+    <row r="81" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C81" s="4"/>
+      <c r="D81" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="E81" s="8">
+      <c r="E81" s="6">
         <v>76</v>
       </c>
     </row>
-    <row r="82" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C82" s="14" t="s">
+    <row r="82" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C82" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="D82" s="8" t="s">
+      <c r="D82" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="E82" s="8">
+      <c r="E82" s="6">
         <v>77</v>
       </c>
     </row>
-    <row r="83" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C83" s="8" t="s">
+    <row r="83" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C83" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="D83" s="8" t="s">
+      <c r="D83" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="E83" s="8">
+      <c r="E83" s="6">
         <v>78</v>
       </c>
     </row>
-    <row r="84" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C84" s="8" t="s">
+    <row r="84" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C84" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="D84" s="8" t="s">
+      <c r="D84" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="E84" s="8">
+      <c r="E84" s="6">
         <v>79</v>
       </c>
     </row>
-    <row r="85" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C85" s="15" t="s">
+    <row r="85" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C85" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="D85" s="8" t="s">
+      <c r="D85" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="E85" s="8">
+      <c r="E85" s="6">
         <v>80</v>
       </c>
     </row>
-    <row r="86" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C86" s="15" t="s">
+    <row r="86" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C86" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="D86" s="8" t="s">
+      <c r="D86" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="E86" s="8">
+      <c r="E86" s="6">
         <v>81</v>
       </c>
     </row>
-    <row r="87" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C87" s="8" t="s">
+    <row r="87" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C87" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="D87" s="15" t="s">
+      <c r="D87" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="E87" s="8">
+      <c r="E87" s="6">
         <v>82</v>
       </c>
     </row>
-    <row r="88" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C88" s="8" t="s">
+    <row r="88" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C88" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="D88" s="15" t="s">
+      <c r="D88" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="E88" s="8">
+      <c r="E88" s="6">
         <v>83</v>
       </c>
     </row>
-    <row r="89" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C89" s="31" t="s">
+    <row r="89" spans="3:5" ht="18" x14ac:dyDescent="0.35">
+      <c r="C89" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="D89" s="31"/>
-      <c r="E89" s="31"/>
-    </row>
-    <row r="90" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C90" s="16"/>
-      <c r="D90" s="7" t="s">
+      <c r="D89" s="5"/>
+      <c r="E89" s="5"/>
+    </row>
+    <row r="90" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C90" s="4"/>
+      <c r="D90" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="E90" s="7">
+      <c r="E90" s="6">
         <v>84</v>
       </c>
     </row>
-    <row r="91" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C91" s="16"/>
-      <c r="D91" s="8" t="s">
+    <row r="91" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C91" s="4"/>
+      <c r="D91" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="E91" s="8">
+      <c r="E91" s="6">
         <v>85</v>
       </c>
     </row>
-    <row r="92" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C92" s="16"/>
-      <c r="D92" s="8" t="s">
+    <row r="92" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C92" s="4"/>
+      <c r="D92" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="E92" s="8">
+      <c r="E92" s="6">
         <v>86</v>
       </c>
     </row>
-    <row r="93" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C93" s="7" t="s">
+    <row r="93" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C93" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D93" s="8" t="s">
+      <c r="D93" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="E93" s="8">
+      <c r="E93" s="6">
         <v>87</v>
       </c>
     </row>
-    <row r="94" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C94" s="8" t="s">
+    <row r="94" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C94" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="D94" s="8" t="s">
+      <c r="D94" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="E94" s="8">
+      <c r="E94" s="6">
         <v>88</v>
       </c>
     </row>
-    <row r="95" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C95" s="7" t="s">
+    <row r="95" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C95" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="D95" s="8" t="s">
+      <c r="D95" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="E95" s="8">
+      <c r="E95" s="6">
         <v>89</v>
       </c>
     </row>
-    <row r="96" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C96" s="8" t="s">
+    <row r="96" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C96" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="D96" s="8" t="s">
+      <c r="D96" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="E96" s="8">
+      <c r="E96" s="6">
         <v>90</v>
       </c>
     </row>
-    <row r="97" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C97" s="9"/>
-      <c r="D97" s="8" t="s">
+    <row r="97" spans="3:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="C97" s="4"/>
+      <c r="D97" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="E97" s="8">
+      <c r="E97" s="6">
         <v>91</v>
       </c>
     </row>
-    <row r="98" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C98" s="7" t="s">
+    <row r="98" spans="3:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="C98" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="D98" s="8" t="s">
+      <c r="D98" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="E98" s="8">
+      <c r="E98" s="6">
         <v>92</v>
       </c>
     </row>
-    <row r="99" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C99" s="8" t="s">
+    <row r="99" spans="3:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="C99" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="D99" s="8" t="s">
+      <c r="D99" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="E99" s="8">
+      <c r="E99" s="6">
         <v>93</v>
       </c>
     </row>
-    <row r="100" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C100" s="8"/>
-      <c r="D100" s="8" t="s">
+    <row r="100" spans="3:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="C100" s="6"/>
+      <c r="D100" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="E100" s="8">
+      <c r="E100" s="6">
         <v>94</v>
       </c>
     </row>
-    <row r="101" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C101" s="8" t="s">
+    <row r="101" spans="3:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="C101" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="D101" s="8" t="s">
+      <c r="D101" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="E101" s="8">
+      <c r="E101" s="6">
         <v>95</v>
       </c>
     </row>
-    <row r="102" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C102" s="8" t="s">
+    <row r="102" spans="3:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="C102" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="D102" s="8" t="s">
+      <c r="D102" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="E102" s="8">
+      <c r="E102" s="6">
         <v>96</v>
       </c>
-      <c r="F102" s="2"/>
-    </row>
-    <row r="103" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C103" s="16"/>
-      <c r="D103" s="8" t="s">
+      <c r="F102" s="1"/>
+    </row>
+    <row r="103" spans="3:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="C103" s="4"/>
+      <c r="D103" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="E103" s="8">
+      <c r="E103" s="6">
         <v>97</v>
       </c>
-      <c r="F103" s="2"/>
-    </row>
-    <row r="104" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C104" s="16"/>
-      <c r="D104" s="8" t="s">
+      <c r="F103" s="1"/>
+    </row>
+    <row r="104" spans="3:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="C104" s="4"/>
+      <c r="D104" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="E104" s="8">
+      <c r="E104" s="6">
         <v>98</v>
       </c>
-      <c r="F104" s="2"/>
-    </row>
-    <row r="105" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C105" s="16" t="s">
+      <c r="F104" s="1"/>
+    </row>
+    <row r="105" spans="3:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="C105" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="D105" s="8" t="s">
+      <c r="D105" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="E105" s="8">
+      <c r="E105" s="6">
         <v>99</v>
       </c>
-      <c r="F105" s="2"/>
-    </row>
-    <row r="106" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C106" s="16"/>
-      <c r="D106" s="8" t="s">
+      <c r="F105" s="1"/>
+    </row>
+    <row r="106" spans="3:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="C106" s="4"/>
+      <c r="D106" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="E106" s="8">
+      <c r="E106" s="6">
         <v>100</v>
       </c>
-      <c r="F106" s="2"/>
-    </row>
-    <row r="107" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C107" s="16"/>
-      <c r="D107" s="8" t="s">
+      <c r="F106" s="1"/>
+    </row>
+    <row r="107" spans="3:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="C107" s="4"/>
+      <c r="D107" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="E107" s="8">
+      <c r="E107" s="6">
         <v>101</v>
       </c>
-      <c r="F107" s="2"/>
-    </row>
-    <row r="108" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C108" s="7" t="s">
+      <c r="F107" s="1"/>
+    </row>
+    <row r="108" spans="3:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="C108" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="D108" s="8" t="s">
+      <c r="D108" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="E108" s="8">
+      <c r="E108" s="6">
         <v>102</v>
       </c>
-      <c r="F108" s="2"/>
-    </row>
-    <row r="109" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C109" s="8" t="s">
+      <c r="F108" s="1"/>
+    </row>
+    <row r="109" spans="3:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="C109" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="D109" s="8" t="s">
+      <c r="D109" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="E109" s="8">
+      <c r="E109" s="6">
         <v>103</v>
       </c>
-      <c r="F109" s="2"/>
-    </row>
-    <row r="110" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C110" s="8" t="s">
+      <c r="F109" s="1"/>
+    </row>
+    <row r="110" spans="3:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="C110" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="D110" s="8" t="s">
+      <c r="D110" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="E110" s="8">
+      <c r="E110" s="6">
         <v>104</v>
       </c>
-      <c r="F110" s="2"/>
-    </row>
-    <row r="111" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C111" s="15" t="s">
+      <c r="F110" s="1"/>
+    </row>
+    <row r="111" spans="3:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="C111" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="D111" s="8" t="s">
+      <c r="D111" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="E111" s="8">
+      <c r="E111" s="6">
         <v>105</v>
       </c>
-      <c r="F111" s="2"/>
-    </row>
-    <row r="112" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C112" s="15"/>
-      <c r="D112" s="8" t="s">
+      <c r="F111" s="1"/>
+    </row>
+    <row r="112" spans="3:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="C112" s="7"/>
+      <c r="D112" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="E112" s="8">
+      <c r="E112" s="6">
         <v>106</v>
       </c>
-      <c r="F112" s="2"/>
-    </row>
-    <row r="113" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C113" s="8" t="s">
+      <c r="F112" s="1"/>
+    </row>
+    <row r="113" spans="3:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="C113" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="D113" s="8" t="s">
+      <c r="D113" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="E113" s="8">
+      <c r="E113" s="6">
         <v>107</v>
       </c>
-      <c r="F113" s="2"/>
-    </row>
-    <row r="114" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C114" s="31" t="s">
+      <c r="F113" s="1"/>
+    </row>
+    <row r="114" spans="3:6" ht="18" x14ac:dyDescent="0.35">
+      <c r="C114" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="D114" s="31"/>
-      <c r="E114" s="31"/>
-      <c r="F114" s="2"/>
-    </row>
-    <row r="115" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C115" s="7" t="s">
+      <c r="D114" s="5"/>
+      <c r="E114" s="5"/>
+      <c r="F114" s="1"/>
+    </row>
+    <row r="115" spans="3:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="C115" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="D115" s="7" t="s">
+      <c r="D115" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="E115" s="8">
+      <c r="E115" s="6">
         <v>108</v>
       </c>
-      <c r="F115" s="2"/>
-    </row>
-    <row r="116" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C116" s="16"/>
-      <c r="D116" s="8" t="s">
+      <c r="F115" s="1"/>
+    </row>
+    <row r="116" spans="3:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="C116" s="4"/>
+      <c r="D116" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="E116" s="8">
+      <c r="E116" s="6">
         <v>109</v>
       </c>
     </row>
-    <row r="117" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C117" s="16"/>
-      <c r="D117" s="8" t="s">
+    <row r="117" spans="3:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="C117" s="4"/>
+      <c r="D117" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="E117" s="8">
+      <c r="E117" s="6">
         <v>110</v>
       </c>
     </row>
-    <row r="118" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C118" s="16"/>
-      <c r="D118" s="8" t="s">
+    <row r="118" spans="3:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="C118" s="4"/>
+      <c r="D118" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="E118" s="8">
+      <c r="E118" s="6">
         <v>111</v>
       </c>
     </row>
-    <row r="119" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C119" s="16" t="s">
+    <row r="119" spans="3:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="C119" s="4" t="s">
         <v>305</v>
       </c>
-      <c r="D119" s="8" t="s">
+      <c r="D119" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="E119" s="8">
+      <c r="E119" s="6">
         <v>112</v>
       </c>
     </row>
-    <row r="120" spans="3:6" ht="34.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C120" s="16" t="s">
+    <row r="120" spans="3:6" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C120" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="D120" s="7" t="s">
+      <c r="D120" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="E120" s="7">
+      <c r="E120" s="6">
         <v>113</v>
       </c>
     </row>
-    <row r="121" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C121" s="16"/>
-      <c r="D121" s="15" t="s">
+    <row r="121" spans="3:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="C121" s="4"/>
+      <c r="D121" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="E121" s="8">
+      <c r="E121" s="6">
         <v>114</v>
       </c>
     </row>
-    <row r="122" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C122" s="16"/>
-      <c r="D122" s="8" t="s">
+    <row r="122" spans="3:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="C122" s="4"/>
+      <c r="D122" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="E122" s="8">
+      <c r="E122" s="6">
         <v>115</v>
       </c>
     </row>
-    <row r="123" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C123" s="16" t="s">
+    <row r="123" spans="3:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="C123" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="D123" s="8" t="s">
+      <c r="D123" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="E123" s="8">
+      <c r="E123" s="6">
         <v>116</v>
       </c>
     </row>
-    <row r="124" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C124" s="16"/>
-      <c r="D124" s="8" t="s">
+    <row r="124" spans="3:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="C124" s="4"/>
+      <c r="D124" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="E124" s="8">
+      <c r="E124" s="6">
         <v>117</v>
       </c>
     </row>
-    <row r="125" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C125" s="16" t="s">
+    <row r="125" spans="3:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="C125" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="D125" s="15" t="s">
+      <c r="D125" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="E125" s="8">
+      <c r="E125" s="6">
         <v>118</v>
       </c>
     </row>
-    <row r="126" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C126" s="7" t="s">
+    <row r="126" spans="3:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="C126" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="D126" s="15" t="s">
+      <c r="D126" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="E126" s="8">
+      <c r="E126" s="6">
         <v>119</v>
       </c>
     </row>
-    <row r="127" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C127" s="7" t="s">
+    <row r="127" spans="3:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="C127" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="D127" s="8" t="s">
+      <c r="D127" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="E127" s="8">
+      <c r="E127" s="6">
         <v>120</v>
       </c>
     </row>
-    <row r="128" spans="3:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C128" s="7" t="s">
+    <row r="128" spans="3:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="C128" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D128" s="8" t="s">
+      <c r="D128" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="E128" s="8">
+      <c r="E128" s="6">
         <v>121</v>
       </c>
     </row>
-    <row r="129" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C129" s="7" t="s">
+    <row r="129" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C129" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="D129" s="8" t="s">
+      <c r="D129" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="E129" s="8">
+      <c r="E129" s="6">
         <v>122</v>
       </c>
     </row>
-    <row r="130" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C130" s="7" t="s">
+    <row r="130" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C130" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="D130" s="8" t="s">
+      <c r="D130" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="E130" s="8">
+      <c r="E130" s="6">
         <v>123</v>
       </c>
     </row>
-    <row r="131" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C131" s="7" t="s">
+    <row r="131" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C131" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="D131" s="8" t="s">
+      <c r="D131" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="E131" s="8">
+      <c r="E131" s="6">
         <v>124</v>
       </c>
     </row>
-    <row r="132" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C132" s="14" t="s">
+    <row r="132" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C132" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="D132" s="8" t="s">
+      <c r="D132" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="E132" s="8">
+      <c r="E132" s="6">
         <v>125</v>
       </c>
     </row>
-    <row r="133" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C133" s="7" t="s">
+    <row r="133" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C133" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="D133" s="15" t="s">
+      <c r="D133" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="E133" s="8">
+      <c r="E133" s="6">
         <v>126</v>
       </c>
     </row>
-    <row r="134" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C134" s="7" t="s">
+    <row r="134" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C134" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="D134" s="15" t="s">
+      <c r="D134" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="E134" s="8">
+      <c r="E134" s="6">
         <v>127</v>
       </c>
     </row>
-    <row r="135" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C135" s="16"/>
-      <c r="D135" s="8" t="s">
+    <row r="135" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C135" s="4"/>
+      <c r="D135" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="E135" s="37">
+      <c r="E135" s="6">
         <v>128</v>
       </c>
     </row>
-    <row r="136" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C136" s="16"/>
-      <c r="D136" s="8" t="s">
+    <row r="136" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C136" s="4"/>
+      <c r="D136" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="E136" s="8">
+      <c r="E136" s="6">
         <v>129</v>
       </c>
     </row>
-    <row r="137" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C137" s="7" t="s">
+    <row r="137" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C137" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="D137" s="8" t="s">
+      <c r="D137" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="E137" s="8">
+      <c r="E137" s="6">
         <v>130</v>
       </c>
     </row>
-    <row r="138" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C138" s="32" t="s">
+    <row r="138" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C138" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="D138" s="32"/>
-      <c r="E138" s="33"/>
-    </row>
-    <row r="139" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C139" s="16" t="s">
+      <c r="D138" s="8"/>
+      <c r="E138" s="8"/>
+    </row>
+    <row r="139" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C139" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="D139" s="7" t="s">
+      <c r="D139" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="E139" s="7">
+      <c r="E139" s="6">
         <v>132</v>
       </c>
     </row>
-    <row r="140" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C140" s="16"/>
-      <c r="D140" s="8" t="s">
+    <row r="140" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C140" s="4"/>
+      <c r="D140" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="E140" s="8">
+      <c r="E140" s="6">
         <v>133</v>
       </c>
     </row>
-    <row r="141" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C141" s="7" t="s">
+    <row r="141" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C141" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="D141" s="7" t="s">
+      <c r="D141" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="E141" s="8">
+      <c r="E141" s="6">
         <v>134</v>
       </c>
     </row>
-    <row r="142" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C142" s="8" t="s">
+    <row r="142" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C142" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="D142" s="8" t="s">
+      <c r="D142" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="E142" s="8">
+      <c r="E142" s="6">
         <v>135</v>
       </c>
     </row>
-    <row r="143" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C143" s="8" t="s">
+    <row r="143" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C143" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="D143" s="8" t="s">
+      <c r="D143" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="E143" s="8">
+      <c r="E143" s="6">
         <v>136</v>
       </c>
     </row>
-    <row r="144" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C144" s="8" t="s">
+    <row r="144" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C144" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="D144" s="8" t="s">
+      <c r="D144" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="E144" s="8">
+      <c r="E144" s="6">
         <v>137</v>
       </c>
     </row>
-    <row r="145" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C145" s="8" t="s">
+    <row r="145" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C145" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="D145" s="8" t="s">
+      <c r="D145" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="E145" s="8">
+      <c r="E145" s="6">
         <v>138</v>
       </c>
     </row>
-    <row r="146" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C146" s="8" t="s">
+    <row r="146" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C146" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="D146" s="8" t="s">
+      <c r="D146" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="E146" s="8">
+      <c r="E146" s="6">
         <v>139</v>
       </c>
     </row>
-    <row r="147" spans="3:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C147" s="8" t="s">
+    <row r="147" spans="3:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C147" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="D147" s="8" t="s">
+      <c r="D147" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="E147" s="8">
+      <c r="E147" s="6">
         <v>140</v>
       </c>
     </row>
-    <row r="148" spans="3:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C148" s="8" t="s">
+    <row r="148" spans="3:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C148" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="D148" s="8" t="s">
+      <c r="D148" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="E148" s="8">
+      <c r="E148" s="6">
         <v>141</v>
       </c>
     </row>
-    <row r="149" spans="3:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C149" s="16" t="s">
+    <row r="149" spans="3:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C149" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="D149" s="15" t="s">
+      <c r="D149" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="E149" s="8">
+      <c r="E149" s="6">
         <v>142</v>
       </c>
     </row>
-    <row r="150" spans="3:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C150" s="9" t="s">
+    <row r="150" spans="3:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C150" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="D150" s="8" t="s">
+      <c r="D150" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="E150" s="8">
+      <c r="E150" s="6">
         <v>143</v>
       </c>
     </row>
-    <row r="151" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C151" s="23"/>
-      <c r="D151" s="11" t="s">
+    <row r="151" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C151" s="4"/>
+      <c r="D151" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="E151" s="8">
+      <c r="E151" s="6">
         <v>144</v>
       </c>
     </row>
-    <row r="152" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C152" s="9" t="s">
+    <row r="152" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C152" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="D152" s="8" t="s">
+      <c r="D152" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="E152" s="8">
+      <c r="E152" s="6">
         <v>145</v>
       </c>
     </row>
-    <row r="153" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C153" s="3" t="s">
+    <row r="153" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C153" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="D153" s="8" t="s">
+      <c r="D153" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="E153" s="8">
+      <c r="E153" s="6">
         <v>146</v>
       </c>
     </row>
-    <row r="154" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C154" s="3" t="s">
+    <row r="154" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C154" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="D154" s="18" t="s">
+      <c r="D154" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="E154" s="8">
+      <c r="E154" s="6">
         <v>147</v>
       </c>
     </row>
-    <row r="155" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C155" s="3" t="s">
+    <row r="155" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C155" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="D155" s="11" t="s">
+      <c r="D155" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="E155" s="8">
+      <c r="E155" s="6">
         <v>148</v>
       </c>
     </row>
-    <row r="156" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C156" s="16" t="s">
+    <row r="156" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C156" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="D156" s="16" t="s">
+      <c r="D156" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="E156" s="8">
+      <c r="E156" s="6">
         <v>149</v>
       </c>
     </row>
-    <row r="157" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C157" s="16"/>
-      <c r="D157" s="10" t="s">
+    <row r="157" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C157" s="4"/>
+      <c r="D157" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="E157" s="8">
+      <c r="E157" s="6">
         <v>150</v>
       </c>
     </row>
-    <row r="158" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C158" s="16" t="s">
+    <row r="158" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C158" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="D158" s="16" t="s">
+      <c r="D158" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="E158" s="8">
+      <c r="E158" s="6">
         <v>151</v>
       </c>
     </row>
-    <row r="159" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C159" s="7" t="s">
+    <row r="159" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C159" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="D159" s="10" t="s">
+      <c r="D159" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="E159" s="8">
+      <c r="E159" s="6">
         <v>152</v>
       </c>
     </row>
-    <row r="160" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C160" s="16"/>
-      <c r="D160" s="11" t="s">
+    <row r="160" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C160" s="4"/>
+      <c r="D160" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="E160" s="8">
+      <c r="E160" s="6">
         <v>153</v>
       </c>
     </row>
-    <row r="161" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C161" s="16"/>
-      <c r="D161" s="11" t="s">
+    <row r="161" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C161" s="4"/>
+      <c r="D161" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="E161" s="8">
+      <c r="E161" s="6">
         <v>154</v>
       </c>
     </row>
-    <row r="162" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C162" s="16"/>
-      <c r="D162" s="11" t="s">
+    <row r="162" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C162" s="4"/>
+      <c r="D162" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="E162" s="8">
+      <c r="E162" s="6">
         <v>155</v>
       </c>
     </row>
-    <row r="163" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C163" s="30" t="s">
+    <row r="163" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C163" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="D163" s="30"/>
-      <c r="E163" s="30"/>
-    </row>
-    <row r="164" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C164" s="16" t="s">
+      <c r="D163" s="9"/>
+      <c r="E163" s="9"/>
+    </row>
+    <row r="164" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C164" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="D164" s="16" t="s">
+      <c r="D164" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="E164" s="1">
+      <c r="E164" s="6">
         <v>156</v>
       </c>
     </row>
-    <row r="165" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C165" s="16" t="s">
+    <row r="165" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C165" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="D165" s="16" t="s">
+      <c r="D165" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="E165" s="1">
+      <c r="E165" s="6">
         <v>157</v>
       </c>
     </row>
-    <row r="166" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C166" s="16" t="s">
+    <row r="166" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C166" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="D166" s="16" t="s">
+      <c r="D166" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="E166" s="1">
+      <c r="E166" s="6">
         <v>158</v>
       </c>
     </row>
-    <row r="167" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C167" s="16"/>
-      <c r="D167" s="16" t="s">
+    <row r="167" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C167" s="4"/>
+      <c r="D167" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="E167" s="1">
+      <c r="E167" s="6">
         <v>159</v>
       </c>
     </row>
-    <row r="168" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C168" s="16"/>
-      <c r="D168" s="16" t="s">
+    <row r="168" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C168" s="4"/>
+      <c r="D168" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="E168" s="1">
+      <c r="E168" s="6">
         <v>160</v>
       </c>
     </row>
-    <row r="169" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C169" s="16" t="s">
+    <row r="169" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C169" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="D169" s="16" t="s">
+      <c r="D169" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="E169" s="1">
+      <c r="E169" s="6">
         <v>161</v>
       </c>
     </row>
-    <row r="170" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C170" s="3" t="s">
+    <row r="170" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C170" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="D170" s="16" t="s">
+      <c r="D170" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="E170" s="1">
+      <c r="E170" s="6">
         <v>162</v>
       </c>
     </row>
-    <row r="171" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C171" s="16" t="s">
+    <row r="171" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C171" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="D171" s="16" t="s">
+      <c r="D171" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="E171" s="1">
+      <c r="E171" s="6">
         <v>163</v>
       </c>
     </row>
-    <row r="172" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C172" s="16" t="s">
+    <row r="172" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C172" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="D172" s="16" t="s">
+      <c r="D172" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="E172" s="1">
+      <c r="E172" s="6">
         <v>164</v>
       </c>
     </row>
-    <row r="173" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C173" s="16" t="s">
+    <row r="173" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C173" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="D173" s="16" t="s">
+      <c r="D173" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="E173" s="1">
+      <c r="E173" s="6">
         <v>165</v>
       </c>
     </row>
-    <row r="174" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C174" s="16" t="s">
+    <row r="174" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C174" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="D174" s="3" t="s">
+      <c r="D174" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="E174" s="1">
+      <c r="E174" s="6">
         <v>166</v>
       </c>
     </row>
-    <row r="175" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C175" s="3" t="s">
+    <row r="175" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C175" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="D175" s="3" t="s">
+      <c r="D175" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="E175" s="1">
+      <c r="E175" s="6">
         <v>167</v>
       </c>
     </row>
-    <row r="176" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C176" s="16"/>
-      <c r="D176" s="5" t="s">
+    <row r="176" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C176" s="4"/>
+      <c r="D176" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="E176" s="3">
+      <c r="E176" s="6">
         <v>168</v>
       </c>
     </row>
-    <row r="177" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C177" s="16"/>
-      <c r="D177" s="3" t="s">
+    <row r="177" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C177" s="4"/>
+      <c r="D177" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="E177" s="3">
+      <c r="E177" s="6">
         <v>169</v>
       </c>
     </row>
-    <row r="178" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C178" s="3" t="s">
+    <row r="178" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C178" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="D178" s="1" t="s">
+      <c r="D178" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="E178" s="3">
+      <c r="E178" s="6">
         <v>170</v>
       </c>
     </row>
-    <row r="179" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C179" s="16"/>
-      <c r="D179" s="1" t="s">
+    <row r="179" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C179" s="4"/>
+      <c r="D179" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="E179" s="3">
+      <c r="E179" s="6">
         <v>171</v>
       </c>
     </row>
-    <row r="180" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C180" s="3" t="s">
+    <row r="180" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C180" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="D180" s="1" t="s">
+      <c r="D180" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="E180" s="3">
+      <c r="E180" s="6">
         <v>172</v>
       </c>
     </row>
-    <row r="181" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C181" s="3" t="s">
+    <row r="181" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C181" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="D181" s="1" t="s">
+      <c r="D181" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="E181" s="3">
+      <c r="E181" s="6">
         <v>173</v>
       </c>
     </row>
-    <row r="182" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C182" s="3" t="s">
+    <row r="182" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C182" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="D182" s="1" t="s">
+      <c r="D182" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="E182" s="3">
+      <c r="E182" s="6">
         <v>174</v>
       </c>
     </row>
-    <row r="183" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C183" s="3" t="s">
+    <row r="183" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C183" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="D183" s="1" t="s">
+      <c r="D183" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="E183" s="3">
+      <c r="E183" s="6">
         <v>175</v>
       </c>
     </row>
-    <row r="184" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C184" s="16" t="s">
+    <row r="184" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C184" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="D184" s="1" t="s">
+      <c r="D184" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="E184" s="3">
+      <c r="E184" s="6">
         <v>176</v>
       </c>
     </row>
-    <row r="185" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C185" s="16"/>
-      <c r="D185" s="1" t="s">
+    <row r="185" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C185" s="4"/>
+      <c r="D185" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="E185" s="3">
+      <c r="E185" s="6">
         <v>177</v>
       </c>
     </row>
-    <row r="186" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C186" s="16"/>
-      <c r="D186" s="1" t="s">
+    <row r="186" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C186" s="4"/>
+      <c r="D186" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="E186" s="3">
+      <c r="E186" s="6">
         <v>178</v>
       </c>
     </row>
     <row r="187" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C187" s="24" t="s">
+      <c r="C187" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="D187" s="25" t="s">
+      <c r="D187" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="E187" s="26">
+      <c r="E187" s="6">
         <v>179</v>
       </c>
     </row>
     <row r="188" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C188" s="29" t="s">
+      <c r="C188" s="9" t="s">
         <v>318</v>
       </c>
-      <c r="D188" s="29"/>
-      <c r="E188" s="29"/>
+      <c r="D188" s="9"/>
+      <c r="E188" s="9"/>
     </row>
     <row r="189" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C189" s="23"/>
-      <c r="D189" s="23" t="s">
+      <c r="C189" s="4"/>
+      <c r="D189" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="E189" s="27">
+      <c r="E189" s="4">
         <v>180</v>
       </c>
     </row>
-    <row r="190" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C190" s="23" t="s">
+    <row r="190" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C190" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="D190" s="23" t="s">
+      <c r="D190" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="E190" s="27">
+      <c r="E190" s="4">
         <v>181</v>
       </c>
     </row>
-    <row r="191" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C191" s="3" t="s">
+    <row r="191" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C191" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="D191" s="23" t="s">
+      <c r="D191" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="E191" s="27">
+      <c r="E191" s="4">
         <v>182</v>
       </c>
     </row>
-    <row r="192" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C192" s="3" t="s">
+    <row r="192" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C192" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="D192" s="28" t="s">
+      <c r="D192" s="6" t="s">
         <v>322</v>
       </c>
-      <c r="E192" s="27">
+      <c r="E192" s="4">
         <v>183</v>
       </c>
     </row>
-    <row r="193" spans="3:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C193" s="23" t="s">
+    <row r="193" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C193" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="D193" s="28" t="s">
+      <c r="D193" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="E193" s="27">
+      <c r="E193" s="4">
         <v>184</v>
       </c>
     </row>
     <row r="194" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C194" s="23" t="s">
+      <c r="C194" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="D194" s="23" t="s">
+      <c r="D194" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="E194" s="27">
+      <c r="E194" s="4">
         <v>185</v>
       </c>
     </row>
     <row r="195" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C195" s="23"/>
-      <c r="D195" s="23" t="s">
+      <c r="C195" s="4"/>
+      <c r="D195" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="E195" s="27">
+      <c r="E195" s="4">
         <v>186</v>
       </c>
     </row>
     <row r="196" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C196" s="23"/>
-      <c r="D196" s="23" t="s">
+      <c r="C196" s="4"/>
+      <c r="D196" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="E196" s="27">
+      <c r="E196" s="4">
         <v>187</v>
       </c>
     </row>
     <row r="197" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C197" s="23"/>
-      <c r="D197" s="23" t="s">
+      <c r="C197" s="4"/>
+      <c r="D197" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="E197" s="27">
+      <c r="E197" s="4">
         <v>188</v>
       </c>
     </row>
     <row r="198" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C198" s="23" t="s">
+      <c r="C198" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="D198" s="23" t="s">
+      <c r="D198" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="E198" s="27">
+      <c r="E198" s="4">
         <v>189</v>
       </c>
     </row>
     <row r="199" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C199" s="23" t="s">
+      <c r="C199" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="D199" s="23" t="s">
+      <c r="D199" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="E199" s="27">
+      <c r="E199" s="4">
         <v>190</v>
       </c>
     </row>
     <row r="200" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C200" s="23" t="s">
+      <c r="C200" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="D200" s="23" t="s">
+      <c r="D200" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="E200" s="27">
+      <c r="E200" s="4">
         <v>191</v>
       </c>
     </row>
     <row r="201" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C201" s="23" t="s">
+      <c r="C201" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="D201" s="23" t="s">
+      <c r="D201" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="E201" s="27">
+      <c r="E201" s="4">
         <v>192</v>
+      </c>
+    </row>
+    <row r="202" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C202" s="4"/>
+      <c r="D202" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="E202" s="4">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="203" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C203" s="4"/>
+      <c r="D203" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="E203" s="4">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="204" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C204" s="4"/>
+      <c r="D204" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="E204" s="4">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="205" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C205" s="4"/>
+      <c r="D205" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="E205" s="4">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="206" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C206" s="4"/>
+      <c r="D206" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="E206" s="4">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="207" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C207" s="4"/>
+      <c r="D207" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="E207" s="4">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="208" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C208" s="4"/>
+      <c r="D208" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="E208" s="4">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="209" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C209" s="4"/>
+      <c r="D209" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="E209" s="4">
+        <v>200</v>
       </c>
     </row>
   </sheetData>

--- a/جدول الحضور-1.xlsx
+++ b/جدول الحضور-1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\E.POINT\Desktop\عيد العرش 2026 جهاد\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33E6C249-257A-4F3B-908C-3540BEAD5C9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4176E93E-5588-4F97-B582-82249EC95A2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{23743375-DD87-4C55-8B35-0449ADC5216E}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="334">
   <si>
     <t>الصفه</t>
   </si>
@@ -304,9 +304,6 @@
   </si>
   <si>
     <t>مدير العلاقات بغرفة التجارة والصناعة والزراعة ببنغازي</t>
-  </si>
-  <si>
-    <t>المستشار العام لغرفة التجارة والصناعة والزراعة ببنغازي</t>
   </si>
   <si>
     <t>مدير مكتب بنغازي بوزارة الخارجية والتعاون الدولي</t>
@@ -1116,19 +1113,19 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1444,7 +1441,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18A94353-2125-49E6-91ED-D3B1232B2558}">
-  <dimension ref="A1:F209"/>
+  <dimension ref="A1:N210"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.88671875" hidden="1" customWidth="1"/>
@@ -1455,1985 +1452,1985 @@
   </cols>
   <sheetData>
     <row r="1" spans="3:5" ht="18" x14ac:dyDescent="0.35">
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
     </row>
     <row r="2" spans="3:5" ht="36" x14ac:dyDescent="0.3">
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="5" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="3" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="E4" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C5" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C6" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C8" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C10" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="3" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C3" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C4" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>282</v>
-      </c>
-      <c r="E4" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C5" s="6" t="s">
+      <c r="E10" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C11" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C12" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C13" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" s="5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C14" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C15" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" s="5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C16" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C17" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" s="5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="3:5" ht="18" x14ac:dyDescent="0.35">
+      <c r="C18" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+    </row>
+    <row r="19" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C19" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" s="6">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C20" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="E20" s="6">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C21" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" s="6">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C22" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E22" s="6">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C23" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E23" s="6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C24" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E24" s="6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C25" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E25" s="6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C26" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E26" s="6">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C27" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E27" s="6">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C28" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E28" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C29" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E29" s="6">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C30" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E30" s="6">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C31" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E31" s="6">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C32" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E32" s="6">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C33" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E33" s="6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C34" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="E34" s="6">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C35" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="E35" s="6">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="36" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C36" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E36" s="6">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C37" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E37" s="6">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="38" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C38" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E38" s="6">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="39" spans="3:5" ht="18" x14ac:dyDescent="0.35">
+      <c r="C39" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
+    </row>
+    <row r="40" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C40" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="D40" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C6" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C7" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C8" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C9" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" s="6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C10" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="E10" s="6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C11" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" s="6">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C12" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E12" s="6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C13" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E13" s="6">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C14" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E14" s="6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C15" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E15" s="6">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C16" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="6">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C17" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E17" s="6">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="3:5" ht="18" x14ac:dyDescent="0.35">
-      <c r="C18" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-    </row>
-    <row r="19" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C19" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E19" s="7">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C20" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="E20" s="7">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C21" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E21" s="7">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C22" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="E22" s="7">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="23" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C23" s="7" t="s">
+      <c r="E40" s="5">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="41" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C41" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="E41" s="5">
         <v>37</v>
       </c>
-      <c r="D23" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E23" s="7">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C24" s="7" t="s">
+    </row>
+    <row r="42" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C42" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="E42" s="5">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="43" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C43" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E43" s="5">
         <v>39</v>
       </c>
-      <c r="D24" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E24" s="7">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="25" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C25" s="7" t="s">
+    </row>
+    <row r="44" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C44" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="E44" s="5">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="45" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C45" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="E45" s="5">
         <v>41</v>
       </c>
-      <c r="D25" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E25" s="7">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C26" s="7" t="s">
+    </row>
+    <row r="46" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C46" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E46" s="5">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="47" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C47" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="E47" s="5">
         <v>43</v>
       </c>
-      <c r="D26" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E26" s="7">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="27" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C27" s="7" t="s">
+    </row>
+    <row r="48" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C48" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E48" s="5">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="49" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C49" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="E49" s="5">
         <v>45</v>
       </c>
-      <c r="D27" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E27" s="7">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="28" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C28" s="7" t="s">
+    </row>
+    <row r="50" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C50" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E50" s="5">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="51" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C51" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E51" s="5">
         <v>47</v>
       </c>
-      <c r="D28" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="E28" s="7">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="29" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C29" s="7" t="s">
+    </row>
+    <row r="52" spans="3:5" ht="36" x14ac:dyDescent="0.3">
+      <c r="C52" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="E52" s="5">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="53" spans="3:5" ht="36" x14ac:dyDescent="0.3">
+      <c r="C53" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E53" s="5">
         <v>49</v>
       </c>
-      <c r="D29" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E29" s="7">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="30" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C30" s="7" t="s">
+    </row>
+    <row r="54" spans="3:5" ht="36" x14ac:dyDescent="0.3">
+      <c r="C54" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="E54" s="5">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="55" spans="3:5" ht="36" x14ac:dyDescent="0.3">
+      <c r="C55" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="E55" s="5">
         <v>51</v>
       </c>
-      <c r="D30" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E30" s="7">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="31" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C31" s="7" t="s">
+    </row>
+    <row r="56" spans="3:5" ht="36" x14ac:dyDescent="0.3">
+      <c r="C56" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="E56" s="5">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="57" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C57" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="E57" s="5">
         <v>53</v>
       </c>
-      <c r="D31" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="E31" s="7">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="32" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C32" s="7" t="s">
+    </row>
+    <row r="58" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C58" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="E58" s="5">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="59" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C59" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E59" s="5">
         <v>55</v>
       </c>
-      <c r="D32" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="E32" s="7">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="33" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C33" s="7" t="s">
+    </row>
+    <row r="60" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C60" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="E60" s="5">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="61" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C61" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="E61" s="5">
         <v>57</v>
       </c>
-      <c r="D33" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="E33" s="7">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="34" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C34" s="7" t="s">
+    </row>
+    <row r="62" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C62" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="E62" s="5">
         <v>58</v>
       </c>
-      <c r="D34" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="E34" s="7">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="35" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C35" s="7" t="s">
+    </row>
+    <row r="63" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C63" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="E63" s="5">
         <v>59</v>
       </c>
-      <c r="D35" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="E35" s="7">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="36" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C36" s="7" t="s">
+    </row>
+    <row r="64" spans="3:5" ht="18" x14ac:dyDescent="0.35">
+      <c r="C64" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="D64" s="7"/>
+      <c r="E64" s="7"/>
+    </row>
+    <row r="65" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C65" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E65" s="5">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="66" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C66" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="E66" s="5">
         <v>61</v>
       </c>
-      <c r="D36" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="E36" s="7">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="37" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C37" s="7" t="s">
+    </row>
+    <row r="67" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C67" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E67" s="5">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="68" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C68" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="E68" s="5">
         <v>63</v>
       </c>
-      <c r="D37" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="E37" s="7">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="38" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C38" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="E38" s="7">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="39" spans="3:5" ht="18" x14ac:dyDescent="0.35">
-      <c r="C39" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D39" s="5"/>
-      <c r="E39" s="5"/>
-    </row>
-    <row r="40" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C40" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="E40" s="6">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="41" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C41" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="E41" s="6">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="42" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C42" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E42" s="6">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="43" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C43" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="D43" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="E43" s="6">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="44" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C44" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="E44" s="6">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="45" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C45" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="D45" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="E45" s="6">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="46" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C46" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="E46" s="6">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="47" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C47" s="6" t="s">
-        <v>289</v>
-      </c>
-      <c r="D47" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="E47" s="6">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="48" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C48" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="E48" s="6">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="49" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C49" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="D49" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="E49" s="6">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="50" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C50" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="D50" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="E50" s="6">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="51" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C51" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="D51" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="E51" s="6">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="52" spans="3:5" ht="36" x14ac:dyDescent="0.3">
-      <c r="C52" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="D52" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="E52" s="6">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="53" spans="3:5" ht="36" x14ac:dyDescent="0.3">
-      <c r="C53" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="D53" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="E53" s="6">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="54" spans="3:5" ht="36" x14ac:dyDescent="0.3">
-      <c r="C54" s="6" t="s">
-        <v>293</v>
-      </c>
-      <c r="D54" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="E54" s="6">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="55" spans="3:5" ht="36" x14ac:dyDescent="0.3">
-      <c r="C55" s="6" t="s">
-        <v>295</v>
-      </c>
-      <c r="D55" s="6" t="s">
-        <v>294</v>
-      </c>
-      <c r="E55" s="6">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="56" spans="3:5" ht="36" x14ac:dyDescent="0.3">
-      <c r="C56" s="6" t="s">
-        <v>295</v>
-      </c>
-      <c r="D56" s="6" t="s">
-        <v>296</v>
-      </c>
-      <c r="E56" s="6">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="57" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C57" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="D57" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="E57" s="6">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="58" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C58" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="D58" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="E58" s="6">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="59" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C59" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D59" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="E59" s="6">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="60" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C60" s="6" t="s">
-        <v>297</v>
-      </c>
-      <c r="D60" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="E60" s="6">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="61" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C61" s="6" t="s">
-        <v>299</v>
-      </c>
-      <c r="D61" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="E61" s="6">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="62" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C62" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="D62" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="E62" s="6">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="63" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C63" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="D63" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="E63" s="6">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="64" spans="3:5" ht="18" x14ac:dyDescent="0.35">
-      <c r="C64" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="D64" s="5"/>
-      <c r="E64" s="5"/>
-    </row>
-    <row r="65" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C65" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="D65" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="E65" s="6">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="66" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C66" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="D66" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="E66" s="6">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="67" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C67" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="D67" s="6" t="s">
-        <v>300</v>
-      </c>
-      <c r="E67" s="6">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="68" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C68" s="6" t="s">
+    </row>
+    <row r="69" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C69" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="D68" s="7" t="s">
+      <c r="D69" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="E68" s="6">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="69" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C69" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="D69" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="E69" s="6">
+      <c r="E69" s="5">
         <v>64</v>
       </c>
     </row>
     <row r="70" spans="3:5" ht="18" x14ac:dyDescent="0.3">
       <c r="C70" s="4"/>
-      <c r="D70" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="E70" s="6">
+      <c r="D70" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="E70" s="5">
         <v>65</v>
       </c>
     </row>
     <row r="71" spans="3:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C71" s="4"/>
-      <c r="D71" s="7" t="s">
+      <c r="D71" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="E71" s="5">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="72" spans="3:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C72" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="D72" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="E71" s="6">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="72" spans="3:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C72" s="6" t="s">
+      <c r="E72" s="5">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="73" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C73" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="D72" s="6" t="s">
+      <c r="D73" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="E72" s="6">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="73" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C73" s="6" t="s">
+      <c r="E73" s="5">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="74" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C74" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="D73" s="6" t="s">
+      <c r="D74" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="E74" s="5">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="75" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C75" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E75" s="5">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="76" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C76" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="D76" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="E76" s="5">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="77" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C77" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D77" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="E77" s="5">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="78" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C78" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="D78" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="E73" s="6">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="74" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C74" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="D74" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="E74" s="6">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="75" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C75" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="D75" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="E75" s="6">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="76" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C76" s="6" t="s">
-        <v>302</v>
-      </c>
-      <c r="D76" s="6" t="s">
-        <v>301</v>
-      </c>
-      <c r="E76" s="6">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="77" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C77" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="D77" s="6" t="s">
+      <c r="E78" s="5">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="79" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C79" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="D79" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="E77" s="6">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="78" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C78" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="D78" s="6" t="s">
-        <v>270</v>
-      </c>
-      <c r="E78" s="6">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="79" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C79" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D79" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="E79" s="6">
+      <c r="E79" s="5">
         <v>74</v>
       </c>
     </row>
     <row r="80" spans="3:5" ht="18" x14ac:dyDescent="0.3">
       <c r="C80" s="4"/>
-      <c r="D80" s="6" t="s">
-        <v>303</v>
-      </c>
-      <c r="E80" s="6">
+      <c r="D80" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="E80" s="5">
         <v>75</v>
       </c>
     </row>
     <row r="81" spans="3:5" ht="18" x14ac:dyDescent="0.3">
       <c r="C81" s="4"/>
-      <c r="D81" s="6" t="s">
+      <c r="D81" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="E81" s="5">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="82" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C82" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D82" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="E81" s="6">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="82" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C82" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="D82" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="E82" s="6">
+      <c r="E82" s="5">
         <v>77</v>
       </c>
     </row>
     <row r="83" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C83" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="D83" s="6" t="s">
+      <c r="C83" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D83" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="E83" s="6">
+      <c r="E83" s="5">
         <v>78</v>
       </c>
     </row>
     <row r="84" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C84" s="6" t="s">
+      <c r="C84" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="D84" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="E84" s="5">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="85" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C85" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="D84" s="6" t="s">
+      <c r="D85" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="E84" s="6">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="85" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C85" s="7" t="s">
+      <c r="E85" s="5">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="86" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C86" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="D85" s="6" t="s">
+      <c r="D86" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="E85" s="6">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="86" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C86" s="7" t="s">
+      <c r="E86" s="5">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="87" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C87" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="D86" s="6" t="s">
+      <c r="D87" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="E86" s="6">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="87" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C87" s="6" t="s">
+      <c r="E87" s="5">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="88" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C88" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="D87" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="E87" s="6">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="88" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C88" s="6" t="s">
+      <c r="D88" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="E88" s="5">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="89" spans="3:5" ht="18" x14ac:dyDescent="0.35">
+      <c r="C89" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="D88" s="7" t="s">
-        <v>304</v>
-      </c>
-      <c r="E88" s="6">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="89" spans="3:5" ht="18" x14ac:dyDescent="0.35">
-      <c r="C89" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="D89" s="5"/>
-      <c r="E89" s="5"/>
+      <c r="D89" s="7"/>
+      <c r="E89" s="7"/>
     </row>
     <row r="90" spans="3:5" ht="18" x14ac:dyDescent="0.3">
       <c r="C90" s="4"/>
-      <c r="D90" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="E90" s="6">
+      <c r="D90" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="E90" s="5">
         <v>84</v>
       </c>
     </row>
     <row r="91" spans="3:5" ht="18" x14ac:dyDescent="0.3">
       <c r="C91" s="4"/>
-      <c r="D91" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="E91" s="6">
+      <c r="D91" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="E91" s="5">
         <v>85</v>
       </c>
     </row>
     <row r="92" spans="3:5" ht="18" x14ac:dyDescent="0.3">
       <c r="C92" s="4"/>
-      <c r="D92" s="6" t="s">
+      <c r="D92" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="E92" s="5">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="93" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C93" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D93" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="E92" s="6">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="93" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C93" s="6" t="s">
+      <c r="E93" s="5">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="94" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C94" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="D93" s="6" t="s">
+      <c r="D94" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="E93" s="6">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="94" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C94" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="D94" s="6" t="s">
+      <c r="E94" s="5">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="95" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C95" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="D95" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="E94" s="6">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="95" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C95" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="D95" s="6" t="s">
+      <c r="E95" s="5">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="96" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C96" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="D96" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="E95" s="6">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="96" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C96" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="D96" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="E96" s="6">
+      <c r="E96" s="5">
         <v>90</v>
       </c>
     </row>
     <row r="97" spans="3:6" ht="18" x14ac:dyDescent="0.3">
       <c r="C97" s="4"/>
-      <c r="D97" s="6" t="s">
+      <c r="D97" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="E97" s="5">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="98" spans="3:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="C98" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="D98" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="E97" s="6">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="98" spans="3:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="C98" s="6" t="s">
+      <c r="E98" s="5">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="99" spans="3:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="C99" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="D98" s="6" t="s">
+      <c r="D99" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="E98" s="6">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="99" spans="3:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="C99" s="6" t="s">
+      <c r="E99" s="5">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="100" spans="3:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="C100" s="5"/>
+      <c r="D100" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="E100" s="5">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="101" spans="3:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="C101" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="D99" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="E99" s="6">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="100" spans="3:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="C100" s="6"/>
-      <c r="D100" s="6" t="s">
+      <c r="D101" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="E100" s="6">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="101" spans="3:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="C101" s="6" t="s">
+      <c r="E101" s="5">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="102" spans="3:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="C102" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="D101" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="E101" s="6">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="102" spans="3:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="C102" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="D102" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="E102" s="6">
+      <c r="D102" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="E102" s="5">
         <v>96</v>
       </c>
       <c r="F102" s="1"/>
     </row>
     <row r="103" spans="3:6" ht="18" x14ac:dyDescent="0.3">
       <c r="C103" s="4"/>
-      <c r="D103" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="E103" s="6">
+      <c r="D103" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="E103" s="5">
         <v>97</v>
       </c>
       <c r="F103" s="1"/>
     </row>
     <row r="104" spans="3:6" ht="18" x14ac:dyDescent="0.3">
       <c r="C104" s="4"/>
-      <c r="D104" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="E104" s="6">
+      <c r="D104" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="E104" s="5">
         <v>98</v>
       </c>
       <c r="F104" s="1"/>
     </row>
     <row r="105" spans="3:6" ht="18" x14ac:dyDescent="0.3">
       <c r="C105" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="D105" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="E105" s="6">
+        <v>167</v>
+      </c>
+      <c r="D105" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="E105" s="5">
         <v>99</v>
       </c>
       <c r="F105" s="1"/>
     </row>
     <row r="106" spans="3:6" ht="18" x14ac:dyDescent="0.3">
       <c r="C106" s="4"/>
-      <c r="D106" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="E106" s="6">
+      <c r="D106" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="E106" s="5">
         <v>100</v>
       </c>
       <c r="F106" s="1"/>
     </row>
     <row r="107" spans="3:6" ht="18" x14ac:dyDescent="0.3">
       <c r="C107" s="4"/>
-      <c r="D107" s="6" t="s">
+      <c r="D107" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="E107" s="5">
+        <v>101</v>
+      </c>
+      <c r="F107" s="1"/>
+    </row>
+    <row r="108" spans="3:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="C108" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="D108" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="E107" s="6">
-        <v>101</v>
-      </c>
-      <c r="F107" s="1"/>
-    </row>
-    <row r="108" spans="3:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="C108" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="D108" s="6" t="s">
+      <c r="E108" s="5">
+        <v>102</v>
+      </c>
+      <c r="F108" s="1"/>
+    </row>
+    <row r="109" spans="3:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="C109" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D109" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E109" s="5">
+        <v>103</v>
+      </c>
+      <c r="F109" s="1"/>
+    </row>
+    <row r="110" spans="3:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="C110" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D110" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E110" s="5">
+        <v>104</v>
+      </c>
+      <c r="F110" s="1"/>
+    </row>
+    <row r="111" spans="3:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="C111" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D111" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E111" s="5">
+        <v>105</v>
+      </c>
+      <c r="F111" s="1"/>
+    </row>
+    <row r="112" spans="3:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="C112" s="6"/>
+      <c r="D112" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="E108" s="6">
-        <v>102</v>
-      </c>
-      <c r="F108" s="1"/>
-    </row>
-    <row r="109" spans="3:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="C109" s="6" t="s">
+      <c r="E112" s="5">
         <v>106</v>
       </c>
-      <c r="D109" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="E109" s="6">
-        <v>103</v>
-      </c>
-      <c r="F109" s="1"/>
-    </row>
-    <row r="110" spans="3:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="C110" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="D110" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="E110" s="6">
-        <v>104</v>
-      </c>
-      <c r="F110" s="1"/>
-    </row>
-    <row r="111" spans="3:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="C111" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="D111" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="E111" s="6">
-        <v>105</v>
-      </c>
-      <c r="F111" s="1"/>
-    </row>
-    <row r="112" spans="3:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="C112" s="7"/>
-      <c r="D112" s="6" t="s">
+      <c r="F112" s="1"/>
+    </row>
+    <row r="113" spans="3:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="C113" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="D113" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="E112" s="6">
-        <v>106</v>
-      </c>
-      <c r="F112" s="1"/>
-    </row>
-    <row r="113" spans="3:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="C113" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="D113" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="E113" s="6">
+      <c r="E113" s="5">
         <v>107</v>
       </c>
       <c r="F113" s="1"/>
     </row>
     <row r="114" spans="3:6" ht="18" x14ac:dyDescent="0.35">
-      <c r="C114" s="5" t="s">
+      <c r="C114" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="D114" s="7"/>
+      <c r="E114" s="7"/>
+      <c r="F114" s="1"/>
+    </row>
+    <row r="115" spans="3:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="C115" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="D114" s="5"/>
-      <c r="E114" s="5"/>
-      <c r="F114" s="1"/>
-    </row>
-    <row r="115" spans="3:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="C115" s="6" t="s">
+      <c r="D115" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="D115" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="E115" s="6">
+      <c r="E115" s="5">
         <v>108</v>
       </c>
       <c r="F115" s="1"/>
     </row>
     <row r="116" spans="3:6" ht="18" x14ac:dyDescent="0.3">
       <c r="C116" s="4"/>
-      <c r="D116" s="6" t="s">
-        <v>272</v>
-      </c>
-      <c r="E116" s="6">
+      <c r="D116" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="E116" s="5">
         <v>109</v>
       </c>
     </row>
     <row r="117" spans="3:6" ht="18" x14ac:dyDescent="0.3">
       <c r="C117" s="4"/>
-      <c r="D117" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="E117" s="6">
+      <c r="D117" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="E117" s="5">
         <v>110</v>
       </c>
     </row>
     <row r="118" spans="3:6" ht="18" x14ac:dyDescent="0.3">
       <c r="C118" s="4"/>
-      <c r="D118" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="E118" s="6">
+      <c r="D118" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="E118" s="5">
         <v>111</v>
       </c>
     </row>
     <row r="119" spans="3:6" ht="18" x14ac:dyDescent="0.3">
       <c r="C119" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="D119" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="E119" s="6">
+        <v>304</v>
+      </c>
+      <c r="D119" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="E119" s="5">
         <v>112</v>
       </c>
     </row>
     <row r="120" spans="3:6" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C120" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="D120" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="E120" s="6">
+        <v>100</v>
+      </c>
+      <c r="D120" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="E120" s="5">
         <v>113</v>
       </c>
     </row>
     <row r="121" spans="3:6" ht="18" x14ac:dyDescent="0.3">
       <c r="C121" s="4"/>
-      <c r="D121" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="E121" s="6">
+      <c r="D121" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="E121" s="5">
         <v>114</v>
       </c>
     </row>
     <row r="122" spans="3:6" ht="18" x14ac:dyDescent="0.3">
       <c r="C122" s="4"/>
-      <c r="D122" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="E122" s="6">
+      <c r="D122" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="E122" s="5">
         <v>115</v>
       </c>
     </row>
     <row r="123" spans="3:6" ht="18" x14ac:dyDescent="0.3">
       <c r="C123" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="D123" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="E123" s="6">
+        <v>197</v>
+      </c>
+      <c r="D123" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="E123" s="5">
         <v>116</v>
       </c>
     </row>
     <row r="124" spans="3:6" ht="18" x14ac:dyDescent="0.3">
       <c r="C124" s="4"/>
-      <c r="D124" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="E124" s="6">
+      <c r="D124" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="E124" s="5">
         <v>117</v>
       </c>
     </row>
     <row r="125" spans="3:6" ht="18" x14ac:dyDescent="0.3">
       <c r="C125" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="D125" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="E125" s="5">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="126" spans="3:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="C126" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="D125" s="7" t="s">
+      <c r="D126" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="E125" s="6">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="126" spans="3:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="C126" s="6" t="s">
+      <c r="E126" s="5">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="127" spans="3:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="C127" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="D126" s="7" t="s">
+      <c r="D127" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="E126" s="6">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="127" spans="3:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="C127" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="D127" s="6" t="s">
+      <c r="E127" s="5">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="128" spans="3:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="C128" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D128" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="E128" s="5">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="129" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C129" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="D129" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="E127" s="6">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="128" spans="3:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="C128" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="D128" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="E128" s="6">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="129" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C129" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="D129" s="6" t="s">
+      <c r="E129" s="5">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="130" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C130" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="D130" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="E129" s="6">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="130" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C130" s="6" t="s">
+      <c r="E130" s="5">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="131" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C131" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="D131" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="E131" s="5">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="132" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C132" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="D132" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="E132" s="5">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="133" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C133" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="D130" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="E130" s="6">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="131" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C131" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="D131" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="E131" s="6">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="132" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C132" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="D132" s="6" t="s">
+      <c r="D133" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="E132" s="6">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="133" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C133" s="6" t="s">
+      <c r="E133" s="5">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="134" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C134" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="D133" s="7" t="s">
+      <c r="D134" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="E133" s="6">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="134" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C134" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="D134" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="E134" s="6">
+      <c r="E134" s="5">
         <v>127</v>
       </c>
     </row>
     <row r="135" spans="3:5" ht="18" x14ac:dyDescent="0.3">
       <c r="C135" s="4"/>
-      <c r="D135" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="E135" s="6">
+      <c r="D135" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="E135" s="5">
         <v>128</v>
       </c>
     </row>
     <row r="136" spans="3:5" ht="18" x14ac:dyDescent="0.3">
       <c r="C136" s="4"/>
-      <c r="D136" s="6" t="s">
+      <c r="D136" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="E136" s="5">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="137" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C137" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="D137" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="E136" s="6">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="137" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C137" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="D137" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="E137" s="6">
+      <c r="E137" s="5">
         <v>130</v>
       </c>
     </row>
     <row r="138" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C138" s="8" t="s">
-        <v>238</v>
-      </c>
-      <c r="D138" s="8"/>
-      <c r="E138" s="8"/>
+      <c r="C138" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="D138" s="9"/>
+      <c r="E138" s="9"/>
     </row>
     <row r="139" spans="3:5" ht="18" x14ac:dyDescent="0.3">
       <c r="C139" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="D139" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="E139" s="6">
+        <v>238</v>
+      </c>
+      <c r="D139" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="E139" s="5">
         <v>132</v>
       </c>
     </row>
     <row r="140" spans="3:5" ht="18" x14ac:dyDescent="0.3">
       <c r="C140" s="4"/>
-      <c r="D140" s="6" t="s">
+      <c r="D140" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="E140" s="5">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="141" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C141" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="D141" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="E140" s="6">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="141" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C141" s="6" t="s">
+      <c r="E141" s="5">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="142" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C142" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="D141" s="6" t="s">
+      <c r="D142" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="E141" s="6">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="142" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C142" s="6" t="s">
+      <c r="E142" s="5">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="143" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C143" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="D142" s="6" t="s">
+      <c r="D143" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="E143" s="5">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="144" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C144" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="D144" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="E142" s="6">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="143" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C143" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="D143" s="6" t="s">
+      <c r="E144" s="5">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="145" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C145" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="D145" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="E145" s="5">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="146" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C146" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="D146" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="E146" s="5">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="147" spans="3:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C147" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="D147" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="E143" s="6">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="144" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C144" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="D144" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="E144" s="6">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="145" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C145" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="D145" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="E145" s="6">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="146" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C146" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="D146" s="6" t="s">
+      <c r="E147" s="5">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="148" spans="3:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C148" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="D148" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="E146" s="6">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="147" spans="3:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C147" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="D147" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="E147" s="6">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="148" spans="3:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C148" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="D148" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="E148" s="6">
+      <c r="E148" s="5">
         <v>141</v>
       </c>
     </row>
     <row r="149" spans="3:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C149" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="D149" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="E149" s="6">
+        <v>231</v>
+      </c>
+      <c r="D149" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="E149" s="5">
         <v>142</v>
       </c>
     </row>
     <row r="150" spans="3:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C150" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="D150" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="E150" s="6">
+        <v>232</v>
+      </c>
+      <c r="D150" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="E150" s="5">
         <v>143</v>
       </c>
     </row>
     <row r="151" spans="3:5" ht="18" x14ac:dyDescent="0.3">
       <c r="C151" s="4"/>
-      <c r="D151" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="E151" s="6">
+      <c r="D151" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="E151" s="5">
         <v>144</v>
       </c>
     </row>
     <row r="152" spans="3:5" ht="18" x14ac:dyDescent="0.3">
       <c r="C152" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="D152" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="E152" s="5">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="153" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C153" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="D152" s="6" t="s">
+      <c r="D153" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="E153" s="5">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="154" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C154" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="D154" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="E152" s="6">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="153" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C153" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="D153" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="E153" s="6">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="154" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C154" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="D154" s="7" t="s">
+      <c r="E154" s="5">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="155" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C155" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="D155" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="E154" s="6">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="155" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C155" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="D155" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="E155" s="6">
+      <c r="E155" s="5">
         <v>148</v>
       </c>
     </row>
     <row r="156" spans="3:5" ht="18" x14ac:dyDescent="0.3">
       <c r="C156" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="E156" s="6">
+        <v>306</v>
+      </c>
+      <c r="E156" s="5">
         <v>149</v>
       </c>
     </row>
     <row r="157" spans="3:5" ht="18" x14ac:dyDescent="0.3">
       <c r="C157" s="4"/>
-      <c r="D157" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="E157" s="6">
+      <c r="D157" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="E157" s="5">
         <v>150</v>
       </c>
     </row>
     <row r="158" spans="3:5" ht="18" x14ac:dyDescent="0.3">
       <c r="C158" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E158" s="6">
+        <v>108</v>
+      </c>
+      <c r="E158" s="5">
         <v>151</v>
       </c>
     </row>
     <row r="159" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C159" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="D159" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="E159" s="6">
+      <c r="C159" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="D159" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="E159" s="5">
         <v>152</v>
       </c>
     </row>
     <row r="160" spans="3:5" ht="18" x14ac:dyDescent="0.3">
       <c r="C160" s="4"/>
-      <c r="D160" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="E160" s="6">
+      <c r="D160" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="E160" s="5">
         <v>153</v>
       </c>
     </row>
     <row r="161" spans="3:5" ht="18" x14ac:dyDescent="0.3">
       <c r="C161" s="4"/>
-      <c r="D161" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="E161" s="6">
+      <c r="D161" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="E161" s="5">
         <v>154</v>
       </c>
     </row>
     <row r="162" spans="3:5" ht="18" x14ac:dyDescent="0.3">
       <c r="C162" s="4"/>
-      <c r="D162" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="E162" s="6">
+      <c r="D162" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="E162" s="5">
         <v>155</v>
       </c>
     </row>
     <row r="163" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C163" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="D163" s="9"/>
-      <c r="E163" s="9"/>
+      <c r="C163" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="D163" s="8"/>
+      <c r="E163" s="8"/>
     </row>
     <row r="164" spans="3:5" ht="18" x14ac:dyDescent="0.3">
       <c r="C164" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="E164" s="6">
+        <v>181</v>
+      </c>
+      <c r="E164" s="5">
         <v>156</v>
       </c>
     </row>
     <row r="165" spans="3:5" ht="18" x14ac:dyDescent="0.3">
       <c r="C165" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="E165" s="6">
+        <v>114</v>
+      </c>
+      <c r="E165" s="5">
         <v>157</v>
       </c>
     </row>
     <row r="166" spans="3:5" ht="18" x14ac:dyDescent="0.3">
       <c r="C166" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="E166" s="6">
+        <v>307</v>
+      </c>
+      <c r="E166" s="5">
         <v>158</v>
       </c>
     </row>
     <row r="167" spans="3:5" ht="18" x14ac:dyDescent="0.3">
       <c r="C167" s="4"/>
       <c r="D167" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="E167" s="6">
+        <v>257</v>
+      </c>
+      <c r="E167" s="5">
         <v>159</v>
       </c>
     </row>
     <row r="168" spans="3:5" ht="18" x14ac:dyDescent="0.3">
       <c r="C168" s="4"/>
       <c r="D168" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="E168" s="6">
+        <v>257</v>
+      </c>
+      <c r="E168" s="5">
         <v>160</v>
       </c>
     </row>
     <row r="169" spans="3:5" ht="18" x14ac:dyDescent="0.3">
       <c r="C169" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="E169" s="6">
+        <v>309</v>
+      </c>
+      <c r="E169" s="5">
         <v>161</v>
       </c>
     </row>
     <row r="170" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C170" s="6" t="s">
-        <v>198</v>
+      <c r="C170" s="5" t="s">
+        <v>197</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="E170" s="6">
+        <v>280</v>
+      </c>
+      <c r="E170" s="5">
         <v>162</v>
       </c>
     </row>
     <row r="171" spans="3:5" ht="18" x14ac:dyDescent="0.3">
       <c r="C171" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="E171" s="6">
+        <v>311</v>
+      </c>
+      <c r="E171" s="5">
         <v>163</v>
       </c>
     </row>
     <row r="172" spans="3:5" ht="18" x14ac:dyDescent="0.3">
       <c r="C172" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="E172" s="6">
+        <v>119</v>
+      </c>
+      <c r="E172" s="5">
         <v>164</v>
       </c>
     </row>
     <row r="173" spans="3:5" ht="18" x14ac:dyDescent="0.3">
       <c r="C173" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="E173" s="6">
+        <v>313</v>
+      </c>
+      <c r="E173" s="5">
         <v>165</v>
       </c>
     </row>
     <row r="174" spans="3:5" ht="18" x14ac:dyDescent="0.3">
       <c r="C174" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="D174" s="6" t="s">
-        <v>315</v>
-      </c>
-      <c r="E174" s="6">
+        <v>201</v>
+      </c>
+      <c r="D174" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="E174" s="5">
         <v>166</v>
       </c>
     </row>
     <row r="175" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C175" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="D175" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="E175" s="6">
+      <c r="C175" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="D175" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="E175" s="5">
         <v>167</v>
       </c>
     </row>
     <row r="176" spans="3:5" ht="18" x14ac:dyDescent="0.3">
       <c r="C176" s="4"/>
       <c r="D176" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="E176" s="6">
+        <v>241</v>
+      </c>
+      <c r="E176" s="5">
         <v>168</v>
       </c>
     </row>
     <row r="177" spans="3:5" ht="18" x14ac:dyDescent="0.3">
       <c r="C177" s="4"/>
-      <c r="D177" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="E177" s="6">
+      <c r="D177" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="E177" s="5">
         <v>169</v>
       </c>
     </row>
     <row r="178" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C178" s="6" t="s">
-        <v>317</v>
-      </c>
-      <c r="D178" s="6" t="s">
+      <c r="C178" s="5" t="s">
         <v>316</v>
       </c>
-      <c r="E178" s="6">
+      <c r="D178" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="E178" s="5">
         <v>170</v>
       </c>
     </row>
     <row r="179" spans="3:5" ht="18" x14ac:dyDescent="0.3">
       <c r="C179" s="4"/>
-      <c r="D179" s="6" t="s">
+      <c r="D179" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="E179" s="5">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="180" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C180" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="D180" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="E179" s="6">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="180" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C180" s="6" t="s">
+      <c r="E180" s="5">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="181" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C181" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="D180" s="6" t="s">
+      <c r="D181" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="E180" s="6">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="181" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C181" s="6" t="s">
+      <c r="E181" s="5">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="182" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C182" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="D182" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="E182" s="5">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="183" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="C183" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="D181" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="E181" s="6">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="182" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C182" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="D182" s="6" t="s">
+      <c r="D183" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="E182" s="6">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="183" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C183" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="D183" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="E183" s="6">
+      <c r="E183" s="5">
         <v>175</v>
       </c>
     </row>
     <row r="184" spans="3:5" ht="18" x14ac:dyDescent="0.3">
       <c r="C184" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="D184" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="D184" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="E184" s="6">
+      <c r="E184" s="5">
         <v>176</v>
       </c>
     </row>
     <row r="185" spans="3:5" ht="18" x14ac:dyDescent="0.3">
       <c r="C185" s="4"/>
-      <c r="D185" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="E185" s="6">
+      <c r="D185" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="E185" s="5">
         <v>177</v>
       </c>
     </row>
     <row r="186" spans="3:5" ht="18" x14ac:dyDescent="0.3">
       <c r="C186" s="4"/>
-      <c r="D186" s="6" t="s">
-        <v>279</v>
-      </c>
-      <c r="E186" s="6">
+      <c r="D186" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="E186" s="5">
         <v>178</v>
       </c>
     </row>
     <row r="187" spans="3:5" ht="18" x14ac:dyDescent="0.3">
       <c r="C187" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="D187" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="E187" s="6">
+        <v>168</v>
+      </c>
+      <c r="D187" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="E187" s="5">
         <v>179</v>
       </c>
     </row>
     <row r="188" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C188" s="9" t="s">
-        <v>318</v>
-      </c>
-      <c r="D188" s="9"/>
-      <c r="E188" s="9"/>
+      <c r="C188" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="D188" s="8"/>
+      <c r="E188" s="8"/>
     </row>
     <row r="189" spans="3:5" ht="18" x14ac:dyDescent="0.3">
       <c r="C189" s="4"/>
       <c r="D189" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E189" s="4">
         <v>180</v>
@@ -3441,200 +3438,204 @@
     </row>
     <row r="190" spans="3:5" ht="18" x14ac:dyDescent="0.3">
       <c r="C190" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D190" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E190" s="4">
         <v>181</v>
       </c>
     </row>
     <row r="191" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C191" s="6" t="s">
-        <v>256</v>
+      <c r="C191" s="5" t="s">
+        <v>255</v>
       </c>
       <c r="D191" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E191" s="4">
         <v>182</v>
       </c>
     </row>
     <row r="192" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C192" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="D192" s="6" t="s">
+      <c r="C192" s="5" t="s">
         <v>322</v>
+      </c>
+      <c r="D192" s="5" t="s">
+        <v>321</v>
       </c>
       <c r="E192" s="4">
         <v>183</v>
       </c>
     </row>
-    <row r="193" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+    <row r="193" spans="3:14" ht="18" x14ac:dyDescent="0.3">
       <c r="C193" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="D193" s="6" t="s">
         <v>324</v>
+      </c>
+      <c r="D193" s="5" t="s">
+        <v>323</v>
       </c>
       <c r="E193" s="4">
         <v>184</v>
       </c>
     </row>
-    <row r="194" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+    <row r="194" spans="3:14" ht="18" x14ac:dyDescent="0.3">
       <c r="C194" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D194" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E194" s="4">
         <v>185</v>
       </c>
     </row>
-    <row r="195" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+    <row r="195" spans="3:14" ht="18" x14ac:dyDescent="0.3">
       <c r="C195" s="4"/>
       <c r="D195" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E195" s="4">
         <v>186</v>
       </c>
     </row>
-    <row r="196" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+    <row r="196" spans="3:14" ht="18" x14ac:dyDescent="0.3">
       <c r="C196" s="4"/>
       <c r="D196" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E196" s="4">
         <v>187</v>
       </c>
     </row>
-    <row r="197" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+    <row r="197" spans="3:14" ht="18" x14ac:dyDescent="0.3">
       <c r="C197" s="4"/>
       <c r="D197" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E197" s="4">
         <v>188</v>
       </c>
     </row>
-    <row r="198" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+    <row r="198" spans="3:14" ht="18" x14ac:dyDescent="0.3">
       <c r="C198" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D198" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E198" s="4">
         <v>189</v>
       </c>
     </row>
-    <row r="199" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+    <row r="199" spans="3:14" ht="18" x14ac:dyDescent="0.3">
       <c r="C199" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D199" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E199" s="4">
         <v>190</v>
       </c>
     </row>
-    <row r="200" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C200" s="4" t="s">
-        <v>228</v>
-      </c>
+    <row r="200" spans="3:14" ht="18" x14ac:dyDescent="0.3">
+      <c r="C200" s="4"/>
       <c r="D200" s="4" t="s">
-        <v>212</v>
+        <v>257</v>
       </c>
       <c r="E200" s="4">
         <v>191</v>
       </c>
     </row>
-    <row r="201" spans="3:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="C201" s="4" t="s">
-        <v>131</v>
-      </c>
+    <row r="201" spans="3:14" ht="18" x14ac:dyDescent="0.3">
+      <c r="C201" s="4"/>
       <c r="D201" s="4" t="s">
-        <v>333</v>
+        <v>257</v>
       </c>
       <c r="E201" s="4">
         <v>192</v>
       </c>
     </row>
-    <row r="202" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+    <row r="202" spans="3:14" ht="18" x14ac:dyDescent="0.3">
       <c r="C202" s="4"/>
       <c r="D202" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E202" s="4">
         <v>193</v>
       </c>
     </row>
-    <row r="203" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+    <row r="203" spans="3:14" ht="18" x14ac:dyDescent="0.3">
       <c r="C203" s="4"/>
       <c r="D203" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E203" s="4">
         <v>194</v>
       </c>
     </row>
-    <row r="204" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+    <row r="204" spans="3:14" ht="18" x14ac:dyDescent="0.3">
       <c r="C204" s="4"/>
       <c r="D204" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E204" s="4">
         <v>195</v>
       </c>
     </row>
-    <row r="205" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+    <row r="205" spans="3:14" ht="18" x14ac:dyDescent="0.3">
       <c r="C205" s="4"/>
       <c r="D205" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E205" s="4">
         <v>196</v>
       </c>
     </row>
-    <row r="206" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+    <row r="206" spans="3:14" ht="18" x14ac:dyDescent="0.3">
       <c r="C206" s="4"/>
       <c r="D206" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E206" s="4">
         <v>197</v>
       </c>
     </row>
-    <row r="207" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+    <row r="207" spans="3:14" ht="18" x14ac:dyDescent="0.3">
       <c r="C207" s="4"/>
       <c r="D207" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E207" s="4">
         <v>198</v>
       </c>
-    </row>
-    <row r="208" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="N207">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="208" spans="3:14" ht="18" x14ac:dyDescent="0.3">
       <c r="C208" s="4"/>
       <c r="D208" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E208" s="4">
         <v>199</v>
       </c>
     </row>
-    <row r="209" spans="3:5" ht="18" x14ac:dyDescent="0.3">
+    <row r="209" spans="3:14" ht="18" x14ac:dyDescent="0.3">
       <c r="C209" s="4"/>
       <c r="D209" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E209" s="4">
         <v>200</v>
+      </c>
+    </row>
+    <row r="210" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="N210">
+        <v>192</v>
       </c>
     </row>
   </sheetData>
